--- a/ig/DM-JUIN-2026/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
+++ b/ig/DM-JUIN-2026/CodeSystem-TRE-R211-ActiviteOperationnelle.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="1511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2171" uniqueCount="1512">
   <si>
     <t>Property</t>
   </si>
@@ -2653,1897 +2653,1900 @@
     <t>370</t>
   </si>
   <si>
+    <t>Soins intensifs spécialisés pédiatrie</t>
+  </si>
+  <si>
+    <t>371</t>
+  </si>
+  <si>
+    <t>Soins intensifs spécialisés néphrologique</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>Soins intensifs spécialisés neurochirurgicaux</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>Surveillance continue polyvalente</t>
+  </si>
+  <si>
+    <t>Activité hospitalière qui assure la surveillance rapprochée de patients présentant un risque de défaillance aiguë d’une ou plusieurs fonctions vitales, sans nécessiter les techniques de suppléance de la réanimation. Elle garantit une présence médicale et infirmière continue, adaptée à l’état clinique du patient.</t>
+  </si>
+  <si>
+    <t>374</t>
+  </si>
+  <si>
+    <t>Surveillance continue chirurgicale</t>
+  </si>
+  <si>
+    <t>375</t>
+  </si>
+  <si>
+    <t>Surveillance continue médicale</t>
+  </si>
+  <si>
+    <t>376</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée cardiologie</t>
+  </si>
+  <si>
+    <t>377</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée neurochirurgie</t>
+  </si>
+  <si>
+    <t>378</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée pneumologie</t>
+  </si>
+  <si>
+    <t>379</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée brûlés</t>
+  </si>
+  <si>
+    <t>380</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée cancérologie oncologie</t>
+  </si>
+  <si>
+    <t>381</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée chirurgie cardiaque et gros vaisseaux</t>
+  </si>
+  <si>
+    <t>382</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée chirurgie thoracique et pulmonaire</t>
+  </si>
+  <si>
+    <t>383</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée chirurgie urologique</t>
+  </si>
+  <si>
+    <t>384</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée chirurgie viscérale et digestive</t>
+  </si>
+  <si>
+    <t>385</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée gynécologie obstétrique</t>
+  </si>
+  <si>
+    <t>386</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée hépato-gastro-entérologie</t>
+  </si>
+  <si>
+    <t>387</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée néphrologique</t>
+  </si>
+  <si>
+    <t>388</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée neurologique</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée chirurgie maxillo-faciale et stomatologie</t>
+  </si>
+  <si>
+    <t>390</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée chirurgie orthopédique et traumatologie</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
+    <t>Surveillance continue spécialisée pédiatrique</t>
+  </si>
+  <si>
+    <t>392</t>
+  </si>
+  <si>
+    <t>Hébergement temporaire d'urgence</t>
+  </si>
+  <si>
+    <t>393</t>
+  </si>
+  <si>
+    <t>Hébergement temporaire d'urgence en sortie d'hospitalisation</t>
+  </si>
+  <si>
+    <t>Les hébergements d'urgence médico-social sont des places, plus ou moins réservées, destinées à des sorties d'hospitalisation de la personne. Ce sont des hébergements très spécifiques et ponctuels dont le but est de mieux préparer le retour à domicile de la personne âgée tout en la maintenant dans un cadre sécurisé avec la présence de soignants ou d'organiser son orientation vers une nouvelle structure d'accueil si nécessaire. Le GT précise que c'est une modalité particulière de l'hébergement temporaire.</t>
+  </si>
+  <si>
+    <t>394</t>
+  </si>
+  <si>
+    <t>Aide au répit (relayage)</t>
+  </si>
+  <si>
+    <t>Ensemble des actes et accompagnements réalisés par des professionnels formés permettant la mise en oeuvre de prestations de suppléance à domicile du proche aidant avec une présence humaine 24h/24h sur une période donnée.</t>
+  </si>
+  <si>
+    <t>395</t>
+  </si>
+  <si>
+    <t>Préparation hospitalière</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>Préparation pour essais cliniques</t>
+  </si>
+  <si>
+    <t>397</t>
+  </si>
+  <si>
+    <t>Pharmacie à Usage Intérieur (PUI)</t>
+  </si>
+  <si>
+    <t>Pharmacie installée au sein d'un groupement hospitalier de territoire ou d'un groupement de coopération sanitaire dans lequel elles ont été constituées établissement de santé, établissements médico-sociaux pour répondre aux besoins pharmaceutiques des personnes prises en charge par ces établissements ou structures.</t>
+  </si>
+  <si>
+    <t>398</t>
+  </si>
+  <si>
+    <t>Stérilisation des dispositifs médicaux</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>Préparation des médicaments radiopharmaceutiques</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Vente de médicaments au public (rétrocession hospitalière)</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>Evaluation du logement et préconisation d'adaptation pour le maintien à domicile</t>
+  </si>
+  <si>
+    <t>Analyse de l’environnement domestique d’une personne en situation de perte d’autonomie, de handicap ou présentant des limitations fonctionnelles, afin d’identifier les obstacles à son maintien à domicile dans des conditions optimales de sécurité, d’autonomie et de qualité de vie. Elle vise à préconiser des aménagements et des aides techniques adaptés, permettant à la personne de réaliser ses activités quotidiennes dans un cadre sécurisé. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>Accompagnement à l'autonomie pour la mobilité et les déplacements</t>
+  </si>
+  <si>
+    <t>Services visant à aider les personnes âgées, handicapées ou atteintes de pathologies chroniques à se déplacer en dehors de leur domicile, favorisant ainsi leur autonomie et leur inclusion sociale. Ces services englobent l'accompagnement dans les transports et l'aide à la mobilité pour les activités quotidiennes, à condition que la prestation soit réalisée à partir ou à destination du domicile, les transports de groupe étant exclus.</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>Apprentissage de l'autonomie pour la vie courante</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>Addictologie avec substance(s)</t>
+  </si>
+  <si>
+    <t>Dépendance qui se caractérise par un désir souvent puissant, voire compulsif, de consommer une substance.</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>Immunothérapie</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>Thérapie ciblée</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>Soins des chambres implantables</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>Chambre mortuaire</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>Oncologie médicale endocrinienne et thyroïdienne</t>
+  </si>
+  <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses des glandes sécrétrices d'hormones : hypophyse, thyroïde, glandes surrénales…</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>Oncologie médicale os et tissus mous</t>
+  </si>
+  <si>
+    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses des tissus mous, sarcome (muscle, graisse, nerf, vaisseaux sanguins…), et des cancers primitifs de l'os.</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>Oncologie métastases osseuses</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>Onco-génétique</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>Exploration et suivi complexe en oncologie et hématologie</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>Soins de support en oncologie et hématologie</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>Transfusion</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>Soins Prolongés Complexes (USPC)</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Neurologie</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>Kinésithérapie Spécialisée Orthopédie</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Respiratoire</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Cardiologie</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Pelvi-périnéologie</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Vasculaire / Lymphatique</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Troubles de l'équilibre</t>
+  </si>
+  <si>
+    <t>424</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Rhumatologie</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Système musculo-squelettique (traumatologie, orthopédie)</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Lésions cutanées et cicatrices (dermatologie, brûlés)</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Sport</t>
+  </si>
+  <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Gériatrie (troubles liés à l'âge)</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>Réunion de Concertation Pluridisciplinaire (RCP) Oncologie pédiatrique</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>Réunion de Concertation Pluridisciplinaire (RCP) cancers rares</t>
+  </si>
+  <si>
+    <t>431</t>
+  </si>
+  <si>
+    <t>Endoscopie broncho-pulmonaire diagnostic</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>Endoscopie broncho-pulmonaire interventionnelle</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>Médecine Transfusionnelle et hémovigilance</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>Elaboration du plan d'aide individualisé</t>
+  </si>
+  <si>
+    <t>résultat de l'action d'expertise menée par des équipes, en général mobiles, qui étudient une situation et déterminent les actions à mettre en oeuvre pour le bénéficiaire, mais ne mènent pas la coordination de la réalisation du plan d'aide.</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>Expertise médicale (évaluation de préjudice)</t>
+  </si>
+  <si>
+    <t>L'expertise médicale est un moyen d'investigation qui éclaire une juridiction ou des parties, sur des questions strictement techniques, et dont la connaissance ou l'explication est nécessaire pour rapporter la vérité ou solutionner un litige. L'expertise médicale a pour but, dans le cadre du dommage corporel ou dans celui des accidents du travail, d'évaluer les séquelles fonctionnelles des victimes d'accidents.</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>Chirurgie du rachis</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>Médecine générale</t>
+  </si>
+  <si>
+    <t>La médecine générale (MG) est la branche de la médecine prenant en charge la prévention, les soins médicaux et le traitement des malades, sans se limiter à des groupes de maladies relevant d'un organe, d'un âge, ou d'un sexe particulier.</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>Accompagnement dans le cadre d'un dispositif d'emploi accompagné (DEA)</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>Gynécologie endocrinienne</t>
+  </si>
+  <si>
+    <t>L'endocrinologie gynécologique comprend la détection et le traitement des maladies hormonales des différentes phases de la vie génitale de la femme.</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>Chirurgie intracrânienne</t>
+  </si>
+  <si>
+    <t>Chirurgie qui comprend l'ouverture du crane pour y réaliser un geste.</t>
+  </si>
+  <si>
+    <t>441</t>
+  </si>
+  <si>
+    <t>Médecine bucco-dentaire</t>
+  </si>
+  <si>
+    <t>Spécialité qui traite les pathologies lourdes ou spécifiques (handicaps, maladies rares…) des mâchoires et des dents.</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>Chirurgie dentaire</t>
+  </si>
+  <si>
+    <t>Discipline qui étudie et traite les affections des dents, des tissus attenants et des mâchoires.</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>Pédodontie ou odontologie pédiatrique</t>
+  </si>
+  <si>
+    <t>Discipline qui étudie et traite les affections des dents, des tissus attenants et des mâchoires chez les enfants et adolescents.</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>Endodontie</t>
+  </si>
+  <si>
+    <t>Discipline de traitement et prévention des atteintes de la pulpe dentaire et des infections périapicales (ou des racines des dents).</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>Biologie moléculaire sur prélèvement Anapath</t>
+  </si>
+  <si>
+    <t>Analyse par des médecins anatomo-pathologistes des prélèvements, par biologie moléculaire avec des techniques ciblées (PCR, RT-PCR, hybridation in situ) ou plus larges (NGS) pour recherche de clonalité, de perte d'hétérozygotie, de mutations, de réarrangements, d'amplifications, à visée diagnostique, pronostique ou théranostique de certaines pathologies tumorales</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>Cytopathologie</t>
+  </si>
+  <si>
+    <t>Etude morphologique des cellules isolées, à partir de produits de ponction, brossage, frottis, aspiration, lavage</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>Histopathologie</t>
+  </si>
+  <si>
+    <t>Etude morphologique des tissus issus d'examen de prélevés par biopsie, ponction-biopsie, résection endoscopique et résection chirurgicale, avec pour objectif d'identifier les lésions provoquées par les maladies ou associées à celles-ci</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>Diagnostic lié à un retard ou Trouble du Neuro-Développement (TND)</t>
+  </si>
+  <si>
+    <t>Diagnostic pour répondre à des besoins relatifs au confort physique, la santé, le bien-être physique et mental.</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>Appui et coopération auprès des acteurs de l'enseignement</t>
+  </si>
+  <si>
+    <t>Soutien des acteurs de l'enseignement, spécialisé ou de droit commun, dans la prise en charge de l'élève, par l'apport d'une expertise et de ressources médico-sociales</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>Accompagnement à la réduction des risques en addictologie</t>
+  </si>
+  <si>
+    <t>Ensemble des pratiques qui visent à réduire les conséquences néfastes de l'addiction, tant au niveau sanitaire, psychologique que social. Cet accompagnement peut être initié par une première évaluation médico-psycho-sociale, et peut par exemple comprendre des ateliers de « pratiques à moindre risque » pour les usagers de drogues</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>Exploration et prise en charge des troubles du sommeil</t>
+  </si>
+  <si>
+    <t>Cette exploration consiste en des examens qui permettent d'enregistrer et d'analyser le sommeil au plan neurologique, respiratoire et cardiologique, ils comprennent entre autres la polysomnographie (correspond à l'exploration nocturne), des tests de maintien d'éveil et des tests de latence d'endormissement correspondent à l'exploration diurne</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>Exploration des troubles psycho-comportementaux et cognitifs</t>
+  </si>
+  <si>
+    <t>Cette exploration comprend une évaluation du fonctionnement cognitif globale (approche psychométrique) et spécifique (évaluation anatomoclinique, mnésique, cognitive, et écologique), une évaluation du comportement (échelles) et la restitution par un compte-rendu</t>
+  </si>
+  <si>
+    <t>453</t>
+  </si>
+  <si>
+    <t>Médecine et santé de l'adolescent</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>Radiologie polyvalente générale</t>
+  </si>
+  <si>
+    <t>Partie de la radiologie réalisant les actes généraux de base de radiologie au sens non hyperspécialisé.</t>
+  </si>
+  <si>
+    <t>455</t>
+  </si>
+  <si>
+    <t>Médecine thermale</t>
+  </si>
+  <si>
+    <t>Ensemble des activités médicales liées à l'utilisation et à l'exploitation des eaux thermales et leurs produits dérivés (gaz, boues), associant la thermalité (chaleur), les techniques de soins et des eaux thermales, à visée thérapeutique</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>Prise en charge médicale spécialisée des affections de l'appareil locomoteur permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections de l'appareil locomoteur sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>Réunion de Concertation Pluridisciplinaire (RCP) Rhumatismes Inflammatoires Chroniques (RIC), maladies auto-immunes et biothérapies en rhumatologie</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>459</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>Réadaptation des affections endocrino-métaboliques et nutrition</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>463</t>
+  </si>
+  <si>
+    <t>Réadaptation des brulés</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>Réadaptation des evc-epr/etats de conscience minimaux</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>Réadaptation des fonctions sexuelles et de la reproduction</t>
+  </si>
+  <si>
+    <t>466</t>
+  </si>
+  <si>
+    <t>Chirurgie des varices</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie vasculaire qui consiste à traiter les maladies des veines superficielles des membres inférieurs ou du pelvis</t>
+  </si>
+  <si>
+    <t>467</t>
+  </si>
+  <si>
+    <t>Chirurgie orthopédique et traumatologique spécialisée main</t>
+  </si>
+  <si>
+    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme), spécialisé dans la chirurgie qui prend en charge les lésions de la main.</t>
+  </si>
+  <si>
+    <t>468</t>
+  </si>
+  <si>
+    <t>Chirurgie orthopédique et traumatologique spécialisée membres inférieurs</t>
+  </si>
+  <si>
+    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les lésions du membre inférieurs</t>
+  </si>
+  <si>
+    <t>469</t>
+  </si>
+  <si>
+    <t>Chirurgie orthopédique et traumatologique spécialisée membres supérieurs (sauf la main)</t>
+  </si>
+  <si>
+    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les lésions du membre supérieur en excluant la main.</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>Chirurgie orthopédique et traumatologique spécialisée tumeur</t>
+  </si>
+  <si>
+    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les tumeurs malignes ou bénignes des os et des tissus mous du membre supérieur et de l'appareil locomoteur</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>Orientation vers un médecin traitant acceptant de nouveaux patients</t>
+  </si>
+  <si>
+    <t>Activité de coordination visant à orienter un patient, en fonction de ses besoins, vers un médecin traitant prenant de nouveaux patients, vers des soins « non programmés » (urgence non vitale) ou encore vers un professionnel de santé disponible (infirmier, dentiste etc.)</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>Veille et prévention de la récidive suicidaire</t>
+  </si>
+  <si>
+    <t>Ce dispositif consiste en un système de recontact et d'alerte en organisant autour de la personne ayant fait une tentative de suicide un réseau de professionnels de santé qui garderont le contact avec elle.</t>
+  </si>
+  <si>
+    <t>473</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique de la sphère oto-rhino-laryngée, cervico-faciale et maxillo-faciale</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses de la sphère oto-rhino-laryngée, cervico-faciale et maxillo-faciale.</t>
+  </si>
+  <si>
+    <t>474</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique viscérale et digestive</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie dont le périmètre d'intervention est l'ensemble des pathologies néoplasiques des organes digestifs et endocriniens, de l'oesophage jusqu'à l'anus.</t>
+  </si>
+  <si>
+    <t>475</t>
+  </si>
+  <si>
+    <t>Coordination de soins non-programmés</t>
+  </si>
+  <si>
+    <t>Organisation de la collaboration des professionnels de santé afin d'améliorer la prise en charge des patients d'une urgence ressentie par le patient, mais ne relevant pas nécessairement d'une urgence médicale à proprement dit.</t>
+  </si>
+  <si>
+    <t>476</t>
+  </si>
+  <si>
+    <t>Exploration fonctionnelle de l'audition</t>
+  </si>
+  <si>
+    <t>Examen(s) destiné(s) à explorer et mesurer le fonctionnement de l'audition.</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>Exploration fonctionnelle de la voix et de la déglutition</t>
+  </si>
+  <si>
+    <t>Examen(s) destiné(s) à apprécier la manière dont un organe assure sa fonction de phonation et de déglutition.</t>
+  </si>
+  <si>
+    <t>478</t>
+  </si>
+  <si>
+    <t>Exploration fonctionnelle des vertiges (audio vestibulaire)</t>
+  </si>
+  <si>
+    <t>Examen(s) destiné(s) à explorer et mesurer la fonction vestibulaire (otoneurologie).</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>Explorations fonctionnelles endocrinologie, diabétologie, métabolisme et nutrition</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>Médecine du sommeil</t>
+  </si>
+  <si>
+    <t>(= hypnologie ou somnologie) est la branche de la médecine spécialisée dans le diagnostic et le traitement des troubles de la vigilance (somnolence excessive) et du sommeil (insomnies, parasomnies).</t>
+  </si>
+  <si>
+    <t>481</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Allergologie</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Allergologie.</t>
+  </si>
+  <si>
+    <t>482</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Andrologie</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Andrologie.</t>
+  </si>
+  <si>
+    <t>483</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Diabétologie</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Diabétologie.</t>
+  </si>
+  <si>
+    <t>484</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Gériatrie, Gérontologie</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Gériatrie, Gérontologie.</t>
+  </si>
+  <si>
+    <t>485</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Gynécologie médicale</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Gynécologie médicale.</t>
+  </si>
+  <si>
+    <t>486</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Maladies infectieuses, parasitaires et tropicales</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Maladies infectieuses, parasitaires et tropicales.</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Médecine pédiatrique</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Médecine pédiatrique.</t>
+  </si>
+  <si>
+    <t>488</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Médecine vasculaire (Angiologie, Phlébologie)</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Médecine vasculaire (Angiologie, Phlébologie).</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Oncogériatrie (cancérologie)</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Oncogériatrie.</t>
+  </si>
+  <si>
+    <t>490</t>
+  </si>
+  <si>
+    <t>Médecine générale à orientation Pathologies osseuses médicales</t>
+  </si>
+  <si>
+    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Pathologies osseuses médicales.</t>
+  </si>
+  <si>
+    <t>491</t>
+  </si>
+  <si>
+    <t>Médecine gériatrique aiguë</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>Neuroradiologie interventionnelle</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau de la sphère cérébrale.</t>
+  </si>
+  <si>
+    <t>493</t>
+  </si>
+  <si>
+    <t>Psychomotricité</t>
+  </si>
+  <si>
+    <t>Aide fournie, sur prescription médicale, à des personnes souffrant de différents troubles psychomoteurs - c'est-à-dire confrontées à des difficultés psychologiques exprimées par le corps - en agissant sur leurs fonctions psychomotrices : difficultés d'attention, problèmes pour se repérer dans l'espace ou dans le temps.</t>
+  </si>
+  <si>
+    <t>494</t>
+  </si>
+  <si>
+    <t>Radiologie abdominale et digestive</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère digestive.</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>Radiologie cardio-vasculaire</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau du coeur et des vaisseaux.</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>Radiologie gynécologique</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère gynécologique.</t>
+  </si>
+  <si>
+    <t>497</t>
+  </si>
+  <si>
+    <t>Radiologie interventionnelle musculosquelettique</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau musculosquelettique.</t>
+  </si>
+  <si>
+    <t>498</t>
+  </si>
+  <si>
+    <t>Radiologie interventionnelle oncologique</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique de pathologies oncologiques.</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
+    <t>Radiologie interventionnelle pédiatrique</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>Radiologie interventionnelle vasculaire</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau des vaisseaux sanguins.</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>Radiologie musculo-squelettique</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau musculo-squelettique.</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>Radiologie ORL et maxillo-faciale</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère ORL et maxillo-faciale.</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>Radiologie prénatale et pédiatrique</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics chez les enfants et en phase prénatale.</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>Radiologie sénologique (dont mammographie)</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau des seins.</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>Radiologie thoracique</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau thoracique.</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>Transplantation d'organe</t>
+  </si>
+  <si>
+    <t>Procédure thérapeutique qui vise à suppléer le fonctionnement défaillant d'un organe par un organe sain, appelé « greffon » ou « transplant » et provenant d'un donneur.</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>Uro-Radiologie</t>
+  </si>
+  <si>
+    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère urogénitale.</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>Exploration fonctionnelle de l'exercice et du sport</t>
+  </si>
+  <si>
+    <t>Ensemble de tests permettant d'évaluer la capacité musculaire à l'effort à des fins de diagnostic, de suivi et de surveillance.</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>Traumatologie de l'activité physique et du sport</t>
+  </si>
+  <si>
+    <t>Prise en charge de l'ensemble des lésions macrotraumatiques et microtraumatiques de l'appareil locomoteur en lien avec la pratique de toute activité physique du niveau loisir au niveau compétition, qu'il s'agisse d'une lésion tendineuse, ligamentaire, osseuse ou cartilagineuse,</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>Échographie obstétricale de dépistage (1er, 2ème, 3ème trimestre)</t>
+  </si>
+  <si>
+    <t>Au premier trimestre : entre 11 semaines et 13 semaines d’aménorrhée et 6 jours (date du début de grossesse, identification et caractérisation des grossesses multiples, évaluation du risque d’anomalie chromosomique, dépistage de certaines pathologies). Au deuxième trimestre : entre 20 et 25 semaines d’aménorrhée (dépistage de certaines pathologies). Au troisième trimestre : entre 30 et 35 semaines d’aménorrhée (dépistage des retards de croissance intra-utérins et de certaines pathologies, localisation du placenta). Il est préférable de programmer ces examens au milieu de ces différentes périodes. Ces examens de dépistage échographique de première intention sont réalisés dans le cadre d’un suivi obstétrical de proximité, par des échographistes expérimentés dont le matériel répond aux normes définies par la nomenclature générale des actes professionnels. Les possibilités réelles et les limites de cet examen doivent être précisées à la femme enceinte ainsi que les informations disponibles dans le compte rendu d’échographie.</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>Accueil et hébergement spécialisé</t>
+  </si>
+  <si>
+    <t>Service qui vise à offrir à un enfant ou un adolescent handicapé un hébergement dans un environnement psychologique, éducatif et affectif complémentaire à celui qu'il peut trouver dans sa propre famille.</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>Accueil et orientation des victimes de violences sexuelles</t>
+  </si>
+  <si>
+    <t>Accueil, aide, soutien et soins aux victimes d'agressions sexuelles</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>Réadaptation locomotrice des patients amputés</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>Réadaptation PREcoce Post-Aiguë Cardiologique (PREPAC)</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>Réadaptation PREcoce Post-Aiguë Respiratoire (PREPAR)</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>Réadaptation neuro-orthopédique</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>Réadaptation PREcoce Post-Aiguë Neurologique (PREPAN)</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>Réadaptation des troubles cognitifs et comportementaux des patients cérébro-lésés</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>Réadaptation des affections médullaires</t>
+  </si>
+  <si>
+    <t>Prise en charge des affections médullaires permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections médullaires sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>Réadaptation de l'obésité complexe</t>
+  </si>
+  <si>
+    <t>Branche des soins médicaux et de réadaptation qui vise à prévenir ou à réduire les conséquences fonctionnelles, les déficiences et les limitations d'activité liées à l'obésité complexe. L'obésité est considérée comme complexe lorsqu'elle présente l'un ou plusieurs des critères suivants : - Excès de poids majeur : indice de masse corporelle (IMC) - Evolution inquiétante de la courbe de corpulence : ascension extrême et continue - Comorbidités sévères associées au surpoids ou à l'obésité : i.e. respiratoires, articulaires, métaboliques, psychologiques ou sociales (harcèlement en milieu scolaire) ; - Antécédents d'échecs thérapeutiques ; - Situation de fragilité : difficultés psychosociales, famille non-aidante, handicap physique et/ou psychique dû à la sévérité de l'obésité, handicap physique non dû à l'obésité mais aggravé par celle-ci, pathologie psychiatrique (utilisation de psychotropes), pathologie chronique (rénale, cardiaque, osseuses, ou autres) aggravée par l'obésité, déficit cognitif, troubles du comportement, pathologie psychiatrique ; - Obésité syndromique identifiée (exemple du syndrome de Prader-Willi) ou non.</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>Réadaptation des troubles cognitifs sévères liés à une conduite addictive</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>Réadaptation polyhandicap</t>
+  </si>
+  <si>
+    <t>Prise en charge du polyhandicap permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections liées au polyhandicap sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
+    <t>523</t>
+  </si>
+  <si>
+    <t>Réadaptation des affections oncologiques</t>
+  </si>
+  <si>
+    <t>524</t>
+  </si>
+  <si>
+    <t>Réadaptation troubles du langage et des apprentissages</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>Evaluation et orientation des auteurs de violences sexuelles</t>
+  </si>
+  <si>
+    <t>526</t>
+  </si>
+  <si>
+    <t>Informer, évaluer, accompagner et orienter dans le cadre d'une orientation professionnelle</t>
+  </si>
+  <si>
+    <t>527</t>
+  </si>
+  <si>
+    <t>Suivi gynécologique de prévention et contraception</t>
+  </si>
+  <si>
+    <t>Consultation gynécologique qui permet les frottis, le dépistage, la prescription d'examens, la prescription de tous les moyens de contraception, de poser et retirer un stérilet ou un implant contraceptif, de pratiquer les IVG médicamenteuses, et de vacciner l'entourage de la femme et du nouveau-né.</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>Suivi neuropsychologique</t>
+  </si>
+  <si>
+    <t>Ensemble des examens, tests et épreuves psychométriques qui permettent de déterminer le retentissement cognitivo-comportemental d'une pathologie connue, de contribuer au diagnostic, ou de contribuer à une expertise médico-légale.</t>
+  </si>
+  <si>
+    <t>529</t>
+  </si>
+  <si>
+    <t>Suivi post-natal (dont séances post-natales)</t>
+  </si>
+  <si>
+    <t>Actions de prévention et de suivi éducatif en cas de besoin particulier décelé pendant la grossesse ou après l'accouchement chez les parents ou chez l'enfant réalisé par les sages-femmes.</t>
+  </si>
+  <si>
+    <t>530</t>
+  </si>
+  <si>
+    <t>Suivi prénatal (suivi de grossesse)</t>
+  </si>
+  <si>
+    <t>Consultations et examens complémentaires qui permettent le suivi de la grossesse normale et l'amélioration de l'identification des situations à risques de complications maternelles, obstétricales et foetales pouvant potentiellement compliquer la grossesse (hors accouchement) afin d'en adapter si besoin le suivi.</t>
+  </si>
+  <si>
+    <t>531</t>
+  </si>
+  <si>
+    <t>Réadaptation viroses chroniques</t>
+  </si>
+  <si>
+    <t>Prise en charge des affections chroniques secondaires à une virose permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>Réadaptation lymphologie</t>
+  </si>
+  <si>
+    <t>Prise en charge des affections dues au lymphoedème permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections sur l'état physique, fonctionnel, mental et social du patient.</t>
+  </si>
+  <si>
+    <t>533</t>
+  </si>
+  <si>
+    <t>Accession à un logement individuel</t>
+  </si>
+  <si>
+    <t>534</t>
+  </si>
+  <si>
+    <t>Accompagnement infirmier pour téléconsultation médicale</t>
+  </si>
+  <si>
+    <t>535</t>
+  </si>
+  <si>
+    <t>Sexologie clinique</t>
+  </si>
+  <si>
+    <t>Etude de la sexualité et de la fonction érotique qui prend en charge les problématiques sexuelles psychologiques, éducationnelles, relationnelles et comportementales</t>
+  </si>
+  <si>
+    <t>536</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique thoracique</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses thoraciques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>537</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique urologique</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses urologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>538</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique gynécologique</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses gynécologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>539</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique mammaire</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses mammaires. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique neurologique</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses neurologiques (intra-crannienne et/ou intra-rachidienne). Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>541</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique ophtalmologique</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses ophtalmologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>542</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique dermatologique</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses dermatologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>543</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique des os et des tissus mous</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses des os et des tissus mous. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>544</t>
+  </si>
+  <si>
+    <t>Chirurgie oncologique de la thyroïde</t>
+  </si>
+  <si>
+    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses de la thyroïde. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
+  </si>
+  <si>
+    <t>545</t>
+  </si>
+  <si>
+    <t>Chimiothérapie intensive</t>
+  </si>
+  <si>
+    <t>546</t>
+  </si>
+  <si>
+    <t>Exploration et prise en charge de la dénutrition</t>
+  </si>
+  <si>
+    <t>Diagnostic et prise en charge d'un état d'un organisme en déséquilibre nutritionnel », le déséquilibre étant caractérisé par un bilan énergétique et/ou protéique négatif soit par un déficit d'apport isolé, une augmentation des dépenses ou des pertes, soit une association d'un déficit d'apport avec une augmentation des dépenses ou des pertes.</t>
+  </si>
+  <si>
+    <t>547</t>
+  </si>
+  <si>
+    <t>Evaluation de situation sociale préoccupante</t>
+  </si>
+  <si>
+    <t>548</t>
+  </si>
+  <si>
+    <t>Coordination de parcours (Care management)</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>Diététique et nutrition</t>
+  </si>
+  <si>
+    <t>Dispensation des conseils nutritionnels  l’éducation et à la rééducation nutritionnelle des patients atteints de troubles du métabolisme ou de l’alimentation, par l’établissement d’un bilan diététique personnalisé et une éducation diététique adaptée. Les diététiciens contribuent à la définition, à l’évaluation et au contrôle de la qualité de l’alimentation servie en collectivité, ainsi qu’aux activités de prévention en santé publique relevant du champ de la nutrition.</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>Accompagnement puériculteur à la périnatalité</t>
+  </si>
+  <si>
+    <t>551</t>
+  </si>
+  <si>
+    <t>Génétique chromosomique</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>Génétique moléculaire</t>
+  </si>
+  <si>
+    <t>553</t>
+  </si>
+  <si>
+    <t>Suivi socio-éducatif</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>Promotion de la santé de l'enfant</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>Soins infirmiers orientation Onco-hématologie</t>
+  </si>
+  <si>
+    <t>556</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en puériculture</t>
+  </si>
+  <si>
+    <t>Ensemble des interventions réalisées par des infirmiers spécialisés diplômés pour promouvoir, maintenir et restaurer la santé des nourrissons, des jeunes enfants et des mères. Ces interventions englobent la prévention, le suivi du développement de l'enfant, l'accompagnement des familles, et les soins spécifiques liés aux pathologies pédiatriques.</t>
+  </si>
+  <si>
+    <t>557</t>
+  </si>
+  <si>
+    <t>Suivi du développement de l'enfant</t>
+  </si>
+  <si>
+    <t>Evaluation continue par un professionnel de santé visant à surveiller la croissance physique, cognitive, émotionnelle et sociale de l'enfant, afin de s'assurer qu'il atteint les étapes clés de son développement en fonction de son âge. Ce suivi permet de dépister précocement d'éventuels retards ou troubles, d'intervenir rapidement si nécessaire et d'accompagner les parents dans leur rôle éducatif et de soutien.</t>
+  </si>
+  <si>
+    <t>558</t>
+  </si>
+  <si>
+    <t>Ergothérapie</t>
+  </si>
+  <si>
+    <t>Activité professionelle qui contribue, par la rééducation, la réadaptation et la réinsertion, au traitement des déficiences, des incapacités et des situations de handicap</t>
+  </si>
+  <si>
+    <t>559</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Fonctions sexuelles et de la reproduction</t>
+  </si>
+  <si>
+    <t>560</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Obésité complexe</t>
+  </si>
+  <si>
+    <t>561</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Cancérologie</t>
+  </si>
+  <si>
+    <t>562</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Pédiatrie</t>
+  </si>
+  <si>
+    <t>563</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Soins palliatifs</t>
+  </si>
+  <si>
+    <t>564</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Santé mentale</t>
+  </si>
+  <si>
+    <t>565</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Maxillo-faciale</t>
+  </si>
+  <si>
+    <t>566</t>
+  </si>
+  <si>
+    <t>Kinésithérapie orientation Gestion de la douleur</t>
+  </si>
+  <si>
+    <t>567</t>
+  </si>
+  <si>
+    <t>Soins infirmiers orientation Gestion de la douleur</t>
+  </si>
+  <si>
+    <t>568</t>
+  </si>
+  <si>
+    <t>Soins infirmiers orientation Santé mentale</t>
+  </si>
+  <si>
+    <t>569</t>
+  </si>
+  <si>
+    <t>Soins infirmiers orientation Cardiologie</t>
+  </si>
+  <si>
+    <t>570</t>
+  </si>
+  <si>
+    <t>Soins infirmiers orientation Respiratoire</t>
+  </si>
+  <si>
+    <t>571</t>
+  </si>
+  <si>
+    <t>Soins infirmiers orientation Soins palliatifs</t>
+  </si>
+  <si>
+    <t>572</t>
+  </si>
+  <si>
+    <t>Soins infirmiers orientation Neurologie</t>
+  </si>
+  <si>
+    <t>573</t>
+  </si>
+  <si>
+    <t>Soins infirmiers orientation Diabète</t>
+  </si>
+  <si>
+    <t>574</t>
+  </si>
+  <si>
+    <t>Ergothérapie orientation accompagnement dans le cadre des maladies chroniques</t>
+  </si>
+  <si>
+    <t>Accompagnement en ergothérapie centré sur l’impact de maladies chroniques (affection de longue durée qui évolue dans le temps, souvent lentement, et qui a un impact durable sur la vie quotidienne de la personne) dans le quotidien de la personne : gestion de la fatigue et/ou la gestion de la douleur et/ou la gestion du sommeil en lien avec les activités de vie la personne dans son environnement. Il vise à favoriser la qualité de vie, l’équilibre de vie.</t>
+  </si>
+  <si>
+    <t>575</t>
+  </si>
+  <si>
+    <t>Ergothérapie orientation compensation matérielle dans l’environnement de la personne</t>
+  </si>
+  <si>
+    <t>Accompagnement en ergothérapie de personnes dans l’accès à l'ensemble des aides techniques, équipements et aménagements destinés à compenser une perte de fonction, une limitation d’activité ou une situation de handicap. Cela inclus l’apprentissage d’utilisation des compensations matérielles et la prise en compte de l’environnement de la personne jusqu’à intervenir dans celui-ci.</t>
+  </si>
+  <si>
+    <t>576</t>
+  </si>
+  <si>
+    <t>Ergothérapie orientation Gériatrie</t>
+  </si>
+  <si>
+    <t>Accompagnement en ergothérapie concerne la prise en charge des personnes âgées, notamment celles confrontées à des pertes d’autonomie, des pathologies chroniques ou neurodégénératives (comme la maladie d'Alzheimer, Parkinson, ou des troubles cognitifs), ainsi qu'à la prévention du vieillissement pathologique. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
+  </si>
+  <si>
+    <t>577</t>
+  </si>
+  <si>
+    <t>Ergothérapie orientation Neurologie</t>
+  </si>
+  <si>
+    <t>Accompagnement en ergothérapie auprès de personnes avec des pathologies neurologiques innées ou acquises (dépistage ; repérage ; évaluation permettant le diagnostic ergothérapique ; réévaluation). Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle.</t>
+  </si>
+  <si>
+    <t>578</t>
+  </si>
+  <si>
+    <t>Ergothérapie orientation Pédiatrie</t>
+  </si>
+  <si>
+    <t>Accompagnement en ergothérapie des enfants, de la naissance à l’adolescence, présentant des troubles du développement, des déficiences physiques, sensorielles, cognitives ou psychiques, ainsi que des situations de handicap, afin de favoriser leur autonomie et leur participation dans les activités de la vie quotidienne, scolaire et sociale. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle.</t>
+  </si>
+  <si>
+    <t>579</t>
+  </si>
+  <si>
+    <t>Ergothérapie orientation Psychiatrie et Santé mentale</t>
+  </si>
+  <si>
+    <t>Accompagnement en ergothérapie  concerne l’accompagnement des personnes présentant des troubles psychiques ou psychiatriques afin de favoriser leur autonomie, leur bien-être et leur inclusion sociale. L’ergothérapeute intervient en évaluant et en renforçant les capacités fonctionnelles, cognitives, émotionnelles et sociales des patients dans le cadre d’un projet thérapeutique global. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
+  </si>
+  <si>
+    <t>580</t>
+  </si>
+  <si>
+    <t>Evaluation en ergothérapie par l’analyse d’activité et accompagnement dans l’environnement de la personne</t>
+  </si>
+  <si>
+    <t>Evaluation fonctionnelle et accompagnement en ergothérapie au travers de mises en situation d’activité réelles (via l’analyse d’activité) en milieu écologique (sur l’ensemble des lieux de vie ((domicile, établissements médico-sociaux, etc.) et d’activité de la personne (établissements scolaires, lieux de formation, milieu professionnel, milieu sportif, de loisirs, etc.)</t>
+  </si>
+  <si>
+    <t>581</t>
+  </si>
+  <si>
+    <t>Interventions éducatives pour renforcer l’autorégulation</t>
+  </si>
+  <si>
+    <t>Consiste à mettre en place des stratégies et des activités visant à aider les personnes, notamment les enfants et les adolescents, à mieux gérer leurs émotions, leurs comportements et leurs pensées. Ces interventions sont particulièrement utiles pour les élèves présentant des troubles du spectre de l'autisme (TSA) et d'autres troubles du neurodéveloppement. Elles sont encadrées par des professionnels, et s'appuient sur des principes de métacognition et d'autodétermination. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
+  </si>
+  <si>
+    <t>582</t>
+  </si>
+  <si>
+    <t>Orientation vers professionnel pour diagnostic</t>
+  </si>
+  <si>
+    <t>583</t>
+  </si>
+  <si>
+    <t>Technique d’épuration extrarénale réalisée au domicile ou en établissement, qui utilise le péritoine comme membrane de dialyse après injection d’une solution de dialyse dans la cavité abdominale, elle constitue une alternative à l’hémodialyse, permettant une autonomie accrue du patient et une efficacité comparable en termes de survie et de qualité de vie.</t>
+  </si>
+  <si>
+    <t>584</t>
+  </si>
+  <si>
+    <t>Diététique des Troubles des Conduites Alimentaires (TCA)</t>
+  </si>
+  <si>
+    <t>Prise en soin diététique  des troubles du comportement alimentaire (anorexie, boulimie, hyperphagie) comprenant  la régulation alimentaire, l’image corporelle et les émotions.</t>
+  </si>
+  <si>
+    <t>585</t>
+  </si>
+  <si>
+    <t>Diététique orientation Dénutrition</t>
+  </si>
+  <si>
+    <t>Accompagnement des patients à risque ou en situation de dénutrition pour prévenir ou corriger les déficits nutritionnels.</t>
+  </si>
+  <si>
+    <t>586</t>
+  </si>
+  <si>
+    <t>Diététique orientation Gynécologie / Obstétrique</t>
+  </si>
+  <si>
+    <t>Prise en charge nutritionnelle des femmes tout au long de leur parcours gynécologique et obstétrique, comprennant  notamment la grossesse, aux parturientes présentant des pathologies spécifiques (diabète gestationnel, troubles métaboliques, surpoids, dénutrition, etc.) ou gynécologique (SOPK, endométriose, ménopause) ou leur grossesse.</t>
+  </si>
+  <si>
+    <t>587</t>
+  </si>
+  <si>
+    <t>Diététique orientation maladies inflammatoires et malabsorptives (MICI, SII, NASH)</t>
+  </si>
+  <si>
+    <t>Prise en charge nutritionnelle individualisée visant à limiter les symptômes, prévenir les carences et adapter l’alimentation selon les phases évolutives de pathologies digestives inflammatoire chroniques.</t>
+  </si>
+  <si>
+    <t>588</t>
+  </si>
+  <si>
+    <t>Diététique orientation Nutrition du sportif</t>
+  </si>
+  <si>
+    <t>Optimisation de l’alimentation pour soutenir la performance, la récupération et la prévention des blessures, chez le sportif  en lien avec les objectifs et le niveau de pratique.</t>
+  </si>
+  <si>
+    <t>589</t>
+  </si>
+  <si>
+    <t>Diététique orientation Périnatalité</t>
+  </si>
+  <si>
+    <t>Soutien nutritionnel dans le cadre du projet parental, de la grossesse, de l’allaitement, et de la diversification alimentaire du nourrisson.</t>
+  </si>
+  <si>
+    <t>590</t>
+  </si>
+  <si>
+    <t>Échographie gynécologique</t>
+  </si>
+  <si>
+    <t>L’échographie gynécologique est un examen d’imagerie médicale par ultrasons destiné à explorer les organes pelviens féminins (principalement l’utérus, l’endomètre, les ovaires, les trompes et les structures annexielles) en dehors du suivi obstétrical. Elle est réalisée par voie endovaginale et/ou par voie sus-pubienne afin de rechercher, caractériser ou suivre des anomalies anatomiques ou pathologiques gynécologiques (telles que kystes ovariens, fibromes, adénomyose, endométriose, etc.) et contribuer à la prise en charge clinique adaptée de la patiente.</t>
+  </si>
+  <si>
+    <t>591</t>
+  </si>
+  <si>
+    <t>Ostéopathie médicale</t>
+  </si>
+  <si>
+    <t>Pratique médicale (réservée aux médecins), utilisant des techniques manuelles de manipulations musculo-squelettiques à visée diagnostique et thérapeutique. L’ostéopathie médicale est reconnue comme acte médical par le Conseil national de l’Ordre des médecins</t>
+  </si>
+  <si>
+    <t>592</t>
+  </si>
+  <si>
+    <t>Prévention et lutte contre la tuberculose</t>
+  </si>
+  <si>
+    <t>593</t>
+  </si>
+  <si>
+    <t>Prise en charge coordonnée des patients atteints de maladies rares</t>
+  </si>
+  <si>
+    <t>Organisation de soins qui dispense  pour les personnes atteintes de maladies rares, un accompagnement pluridisciplinaire, depuis le diagnostic jusqu’au suivi, impliquant professionnels spécialisés, de proximité, médico-social, social et associations.</t>
+  </si>
+  <si>
+    <t>594</t>
+  </si>
+  <si>
+    <t>Coordination hospitalière de prélèvement de tissu</t>
+  </si>
+  <si>
+    <t>Activité hospitalière spécialisée qui coordonne l’ensemble des prélèvements de tissu (et d’organe), assure le recueil de la non-opposition, l’accompagnement des proches, la traçabilité, la sécurité sanitaire et le respect des règles légales et éthiques.</t>
+  </si>
+  <si>
+    <t>595</t>
+  </si>
+  <si>
+    <t>Coordination hospitalière de prélèvement de tissu pédiatrique</t>
+  </si>
+  <si>
+    <t>Activité hospitalière spécialisée qui organise le prélèvement de tissu chez des enfants (vivants ou décédés), la recherche du consentement éclairé des représentants légaux, la traçabilité, et les règles juridiques et éthiques propres au don de tissus.</t>
+  </si>
+  <si>
+    <t>596</t>
+  </si>
+  <si>
+    <t>Coordination hospitalière de prélèvement d’organe pédiatrique</t>
+  </si>
+  <si>
+    <t>Activité hospitalière spécialisée qui identifie, mobilise et coordonne les prélèvements d’organes chez les enfants, en assurant le recueil du consentement légal, la conformité aux règles éthiques, la traçabilité et la liaison entre les équipes de greffe et les proches.</t>
+  </si>
+  <si>
+    <t>597</t>
+  </si>
+  <si>
+    <t>Evaluation de la mémoire (bilan mémoire)</t>
+  </si>
+  <si>
+    <t>Evaluation clinique spécialisée qui mesure de façon formelle les capacités mnésiques  (encodage, stockage, restitution ) et recherche leur retentissement sur la vie quotidienne, à l’aide de tests validés, d’un entretien, et d’examens complémentaires afin de poser un diagnostic ou d’orienter vers une prise en charge adaptée.</t>
+  </si>
+  <si>
+    <t>598</t>
+  </si>
+  <si>
+    <t>Toxicologie clinique</t>
+  </si>
+  <si>
+    <t>599</t>
+  </si>
+  <si>
+    <t>Analyse toxicologique</t>
+  </si>
+  <si>
+    <t>600</t>
+  </si>
+  <si>
+    <t>Prise en charge des malaises et surdoses liés à la prise de drogues</t>
+  </si>
+  <si>
+    <t>601</t>
+  </si>
+  <si>
+    <t>Médiation pour le maintien en hospitalisation</t>
+  </si>
+  <si>
+    <t>602</t>
+  </si>
+  <si>
+    <t>Pair aidance pour l'autodétermination</t>
+  </si>
+  <si>
+    <t>603</t>
+  </si>
+  <si>
+    <t>Prise en charge coordonnée des patients atteints de maladies neurodégénératives</t>
+  </si>
+  <si>
+    <t>604</t>
+  </si>
+  <si>
+    <t>Chirurgie pédiatrique spécialisée orthopédique</t>
+  </si>
+  <si>
+    <t>605</t>
+  </si>
+  <si>
+    <t>Chirurgie pédiatrique spécialisée digestif et viscérale</t>
+  </si>
+  <si>
+    <t>606</t>
+  </si>
+  <si>
+    <t>Accompagnement pour l’autodétermination de la personne</t>
+  </si>
+  <si>
+    <t>607</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès des acteurs du secteur sanitaire</t>
+  </si>
+  <si>
+    <t>608</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès des acteurs du milieu ordinaire</t>
+  </si>
+  <si>
+    <t>609</t>
+  </si>
+  <si>
+    <t>Fonction-ressource : expertise-conseils auprès de acteurs du secteur judiciaire</t>
+  </si>
+  <si>
+    <t>610</t>
+  </si>
+  <si>
+    <t>Pédiatrie spécialisée neurologie</t>
+  </si>
+  <si>
+    <t>611</t>
+  </si>
+  <si>
+    <t>Pédiatrie spécialisée pneumologie</t>
+  </si>
+  <si>
+    <t>612</t>
+  </si>
+  <si>
+    <t>Psychiatrie de crise</t>
+  </si>
+  <si>
+    <t>Activité de soins psychiatriques qui assure une prise en charge immédiate des situations de crise psychique aiguë, caractérisées par une souffrance intense ou un risque pour la personne, afin de prévenir une aggravation ou une hospitalisation non adaptée. Elle s’appuie sur des interventions brèves, coordonnées et pluridisciplinaires, en lien avec les dispositifs d’urgence.</t>
+  </si>
+  <si>
+    <t>613</t>
+  </si>
+  <si>
+    <t>Echographie obstétricale de diagnostic</t>
+  </si>
+  <si>
+    <t>En cas d’aspect inhabituel (morphologique et/ou biométrique), de doute ou de difficulté persistante à fournir les éléments demandés pour l’examen de dépistage. Cet examen de deuxième rang est réalisé par des praticiens ayant une expérience et une expertise spécifiques et exerçant en relation avec un (ou plusieurs) Centre(s) Pluridisciplinaire(s) de Diagnostic Prénatal.</t>
+  </si>
+  <si>
+    <t>614</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en pathologies chroniques stabilisées</t>
+  </si>
+  <si>
+    <t>615</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en oncologie et hémato-oncologie</t>
+  </si>
+  <si>
+    <t>616</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en maladie rénale chronique</t>
+  </si>
+  <si>
+    <t>617</t>
+  </si>
+  <si>
+    <t>Soins infirmiers en pratique avancée en santé mentale</t>
+  </si>
+  <si>
+    <t>618</t>
+  </si>
+  <si>
+    <t>Collecte de don de lait maternel cru</t>
+  </si>
+  <si>
+    <t>619</t>
+  </si>
+  <si>
+    <t>Distribution de lait maternel pasteurisé</t>
+  </si>
+  <si>
+    <t>620</t>
+  </si>
+  <si>
+    <t>Bilan psychomoteur</t>
+  </si>
+  <si>
+    <t>621</t>
+  </si>
+  <si>
+    <t>Soin psychomoteur</t>
+  </si>
+  <si>
+    <t>622</t>
+  </si>
+  <si>
+    <t>Education psychomotrice (pédagogie du développement psychomoteur)</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>Stimulation psychomotrice (stimulation du fonctionnement psychomoteur à visée préventive)</t>
+  </si>
+  <si>
+    <t>624</t>
+  </si>
+  <si>
+    <t>Rééducation de la graphomotricité et de l’écriture (dysgraphie)</t>
+  </si>
+  <si>
+    <t>625</t>
+  </si>
+  <si>
+    <t>Orthoptie : orientation troubles neuro-visuels (pathologies neurologiques, maladies neurodégénératives)</t>
+  </si>
+  <si>
+    <t>626</t>
+  </si>
+  <si>
+    <t>Orthoptie orientation basse vision</t>
+  </si>
+  <si>
+    <t>627</t>
+  </si>
+  <si>
+    <t>Orthoptie orientation pédiatrique</t>
+  </si>
+  <si>
+    <t>628</t>
+  </si>
+  <si>
     <t>Dispensation de médicaments et autres produits de santé appartenant au monopole pharmaceutique</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>Soins intensifs spécialisés néphrologique</t>
-  </si>
-  <si>
-    <t>372</t>
-  </si>
-  <si>
-    <t>Soins intensifs spécialisés neurochirurgicaux</t>
-  </si>
-  <si>
-    <t>373</t>
-  </si>
-  <si>
-    <t>Surveillance continue polyvalente</t>
-  </si>
-  <si>
-    <t>Activité hospitalière qui assure la surveillance rapprochée de patients présentant un risque de défaillance aiguë d’une ou plusieurs fonctions vitales, sans nécessiter les techniques de suppléance de la réanimation. Elle garantit une présence médicale et infirmière continue, adaptée à l’état clinique du patient.</t>
-  </si>
-  <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>Surveillance continue chirurgicale</t>
-  </si>
-  <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>Surveillance continue médicale</t>
-  </si>
-  <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée cardiologie</t>
-  </si>
-  <si>
-    <t>377</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée neurochirurgie</t>
-  </si>
-  <si>
-    <t>378</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée pneumologie</t>
-  </si>
-  <si>
-    <t>379</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée brûlés</t>
-  </si>
-  <si>
-    <t>380</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée cancérologie oncologie</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée chirurgie cardiaque et gros vaisseaux</t>
-  </si>
-  <si>
-    <t>382</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée chirurgie thoracique et pulmonaire</t>
-  </si>
-  <si>
-    <t>383</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée chirurgie urologique</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée chirurgie viscérale et digestive</t>
-  </si>
-  <si>
-    <t>385</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée gynécologie obstétrique</t>
-  </si>
-  <si>
-    <t>386</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée hépato-gastro-entérologie</t>
-  </si>
-  <si>
-    <t>387</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée néphrologique</t>
-  </si>
-  <si>
-    <t>388</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée neurologique</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée chirurgie maxillo-faciale et stomatologie</t>
-  </si>
-  <si>
-    <t>390</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée chirurgie orthopédique et traumatologie</t>
-  </si>
-  <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>Surveillance continue spécialisée pédiatrique</t>
-  </si>
-  <si>
-    <t>392</t>
-  </si>
-  <si>
-    <t>Hébergement temporaire d'urgence</t>
-  </si>
-  <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>Hébergement temporaire d'urgence en sortie d'hospitalisation</t>
-  </si>
-  <si>
-    <t>Les hébergements d'urgence médico-social sont des places, plus ou moins réservées, destinées à des sorties d'hospitalisation de la personne. Ce sont des hébergements très spécifiques et ponctuels dont le but est de mieux préparer le retour à domicile de la personne âgée tout en la maintenant dans un cadre sécurisé avec la présence de soignants ou d'organiser son orientation vers une nouvelle structure d'accueil si nécessaire. Le GT précise que c'est une modalité particulière de l'hébergement temporaire.</t>
-  </si>
-  <si>
-    <t>394</t>
-  </si>
-  <si>
-    <t>Aide au répit (relayage)</t>
-  </si>
-  <si>
-    <t>Ensemble des actes et accompagnements réalisés par des professionnels formés permettant la mise en oeuvre de prestations de suppléance à domicile du proche aidant avec une présence humaine 24h/24h sur une période donnée.</t>
-  </si>
-  <si>
-    <t>395</t>
-  </si>
-  <si>
-    <t>Préparation hospitalière</t>
-  </si>
-  <si>
-    <t>396</t>
-  </si>
-  <si>
-    <t>Préparation pour essais cliniques</t>
-  </si>
-  <si>
-    <t>397</t>
-  </si>
-  <si>
-    <t>Pharmacie à Usage Intérieur (PUI)</t>
-  </si>
-  <si>
-    <t>Pharmacie installée au sein d'un groupement hospitalier de territoire ou d'un groupement de coopération sanitaire dans lequel elles ont été constituées établissement de santé, établissements médico-sociaux pour répondre aux besoins pharmaceutiques des personnes prises en charge par ces établissements ou structures.</t>
-  </si>
-  <si>
-    <t>398</t>
-  </si>
-  <si>
-    <t>Stérilisation des dispositifs médicaux</t>
-  </si>
-  <si>
-    <t>399</t>
-  </si>
-  <si>
-    <t>Préparation des médicaments radiopharmaceutiques</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>Vente de médicaments au public (rétrocession hospitalière)</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>Evaluation du logement et préconisation d'adaptation pour le maintien à domicile</t>
-  </si>
-  <si>
-    <t>Analyse de l’environnement domestique d’une personne en situation de perte d’autonomie, de handicap ou présentant des limitations fonctionnelles, afin d’identifier les obstacles à son maintien à domicile dans des conditions optimales de sécurité, d’autonomie et de qualité de vie. Elle vise à préconiser des aménagements et des aides techniques adaptés, permettant à la personne de réaliser ses activités quotidiennes dans un cadre sécurisé. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
-  </si>
-  <si>
-    <t>402</t>
-  </si>
-  <si>
-    <t>Accompagnement à l'autonomie pour la mobilité et les déplacements</t>
-  </si>
-  <si>
-    <t>Services visant à aider les personnes âgées, handicapées ou atteintes de pathologies chroniques à se déplacer en dehors de leur domicile, favorisant ainsi leur autonomie et leur inclusion sociale. Ces services englobent l'accompagnement dans les transports et l'aide à la mobilité pour les activités quotidiennes, à condition que la prestation soit réalisée à partir ou à destination du domicile, les transports de groupe étant exclus.</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>Apprentissage de l'autonomie pour la vie courante</t>
-  </si>
-  <si>
-    <t>404</t>
-  </si>
-  <si>
-    <t>Addictologie avec substance(s)</t>
-  </si>
-  <si>
-    <t>Dépendance qui se caractérise par un désir souvent puissant, voire compulsif, de consommer une substance.</t>
-  </si>
-  <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>Immunothérapie</t>
-  </si>
-  <si>
-    <t>406</t>
-  </si>
-  <si>
-    <t>Thérapie ciblée</t>
-  </si>
-  <si>
-    <t>407</t>
-  </si>
-  <si>
-    <t>Soins des chambres implantables</t>
-  </si>
-  <si>
-    <t>408</t>
-  </si>
-  <si>
-    <t>Chambre mortuaire</t>
-  </si>
-  <si>
-    <t>409</t>
-  </si>
-  <si>
-    <t>Oncologie médicale endocrinienne et thyroïdienne</t>
-  </si>
-  <si>
-    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses des glandes sécrétrices d'hormones : hypophyse, thyroïde, glandes surrénales…</t>
-  </si>
-  <si>
-    <t>410</t>
-  </si>
-  <si>
-    <t>Oncologie médicale os et tissus mous</t>
-  </si>
-  <si>
-    <t>Branche de l'oncologie médicale qui s'intéresse aux tumeurs cancéreuses des tissus mous, sarcome (muscle, graisse, nerf, vaisseaux sanguins…), et des cancers primitifs de l'os.</t>
-  </si>
-  <si>
-    <t>411</t>
-  </si>
-  <si>
-    <t>Oncologie métastases osseuses</t>
-  </si>
-  <si>
-    <t>412</t>
-  </si>
-  <si>
-    <t>Onco-génétique</t>
-  </si>
-  <si>
-    <t>413</t>
-  </si>
-  <si>
-    <t>Exploration et suivi complexe en oncologie et hématologie</t>
-  </si>
-  <si>
-    <t>414</t>
-  </si>
-  <si>
-    <t>Soins de support en oncologie et hématologie</t>
-  </si>
-  <si>
-    <t>415</t>
-  </si>
-  <si>
-    <t>Transfusion</t>
-  </si>
-  <si>
-    <t>416</t>
-  </si>
-  <si>
-    <t>Soins Prolongés Complexes (USPC)</t>
-  </si>
-  <si>
-    <t>417</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Neurologie</t>
-  </si>
-  <si>
-    <t>418</t>
-  </si>
-  <si>
-    <t>Kinésithérapie Spécialisée Orthopédie</t>
-  </si>
-  <si>
-    <t>419</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Respiratoire</t>
-  </si>
-  <si>
-    <t>420</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Cardiologie</t>
-  </si>
-  <si>
-    <t>421</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Pelvi-périnéologie</t>
-  </si>
-  <si>
-    <t>422</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Vasculaire / Lymphatique</t>
-  </si>
-  <si>
-    <t>423</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Troubles de l'équilibre</t>
-  </si>
-  <si>
-    <t>424</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Rhumatologie</t>
-  </si>
-  <si>
-    <t>425</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Système musculo-squelettique (traumatologie, orthopédie)</t>
-  </si>
-  <si>
-    <t>426</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Lésions cutanées et cicatrices (dermatologie, brûlés)</t>
-  </si>
-  <si>
-    <t>427</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Sport</t>
-  </si>
-  <si>
-    <t>428</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Gériatrie (troubles liés à l'âge)</t>
-  </si>
-  <si>
-    <t>429</t>
-  </si>
-  <si>
-    <t>Réunion de Concertation Pluridisciplinaire (RCP) Oncologie pédiatrique</t>
-  </si>
-  <si>
-    <t>430</t>
-  </si>
-  <si>
-    <t>Réunion de Concertation Pluridisciplinaire (RCP) cancers rares</t>
-  </si>
-  <si>
-    <t>431</t>
-  </si>
-  <si>
-    <t>Endoscopie broncho-pulmonaire diagnostic</t>
-  </si>
-  <si>
-    <t>432</t>
-  </si>
-  <si>
-    <t>Endoscopie broncho-pulmonaire interventionnelle</t>
-  </si>
-  <si>
-    <t>433</t>
-  </si>
-  <si>
-    <t>Médecine Transfusionnelle et hémovigilance</t>
-  </si>
-  <si>
-    <t>434</t>
-  </si>
-  <si>
-    <t>Elaboration du plan d'aide individualisé</t>
-  </si>
-  <si>
-    <t>résultat de l'action d'expertise menée par des équipes, en général mobiles, qui étudient une situation et déterminent les actions à mettre en oeuvre pour le bénéficiaire, mais ne mènent pas la coordination de la réalisation du plan d'aide.</t>
-  </si>
-  <si>
-    <t>435</t>
-  </si>
-  <si>
-    <t>Expertise médicale (évaluation de préjudice)</t>
-  </si>
-  <si>
-    <t>L'expertise médicale est un moyen d'investigation qui éclaire une juridiction ou des parties, sur des questions strictement techniques, et dont la connaissance ou l'explication est nécessaire pour rapporter la vérité ou solutionner un litige. L'expertise médicale a pour but, dans le cadre du dommage corporel ou dans celui des accidents du travail, d'évaluer les séquelles fonctionnelles des victimes d'accidents.</t>
-  </si>
-  <si>
-    <t>436</t>
-  </si>
-  <si>
-    <t>Chirurgie du rachis</t>
-  </si>
-  <si>
-    <t>437</t>
-  </si>
-  <si>
-    <t>Médecine générale</t>
-  </si>
-  <si>
-    <t>La médecine générale (MG) est la branche de la médecine prenant en charge la prévention, les soins médicaux et le traitement des malades, sans se limiter à des groupes de maladies relevant d'un organe, d'un âge, ou d'un sexe particulier.</t>
-  </si>
-  <si>
-    <t>438</t>
-  </si>
-  <si>
-    <t>Accompagnement dans le cadre d'un dispositif d'emploi accompagné (DEA)</t>
-  </si>
-  <si>
-    <t>439</t>
-  </si>
-  <si>
-    <t>Gynécologie endocrinienne</t>
-  </si>
-  <si>
-    <t>L'endocrinologie gynécologique comprend la détection et le traitement des maladies hormonales des différentes phases de la vie génitale de la femme.</t>
-  </si>
-  <si>
-    <t>440</t>
-  </si>
-  <si>
-    <t>Chirurgie intracrânienne</t>
-  </si>
-  <si>
-    <t>Chirurgie qui comprend l'ouverture du crane pour y réaliser un geste.</t>
-  </si>
-  <si>
-    <t>441</t>
-  </si>
-  <si>
-    <t>Médecine bucco-dentaire</t>
-  </si>
-  <si>
-    <t>Spécialité qui traite les pathologies lourdes ou spécifiques (handicaps, maladies rares…) des mâchoires et des dents.</t>
-  </si>
-  <si>
-    <t>442</t>
-  </si>
-  <si>
-    <t>Chirurgie dentaire</t>
-  </si>
-  <si>
-    <t>Discipline qui étudie et traite les affections des dents, des tissus attenants et des mâchoires.</t>
-  </si>
-  <si>
-    <t>443</t>
-  </si>
-  <si>
-    <t>Pédodontie ou odontologie pédiatrique</t>
-  </si>
-  <si>
-    <t>Discipline qui étudie et traite les affections des dents, des tissus attenants et des mâchoires chez les enfants et adolescents.</t>
-  </si>
-  <si>
-    <t>444</t>
-  </si>
-  <si>
-    <t>Endodontie</t>
-  </si>
-  <si>
-    <t>Discipline de traitement et prévention des atteintes de la pulpe dentaire et des infections périapicales (ou des racines des dents).</t>
-  </si>
-  <si>
-    <t>445</t>
-  </si>
-  <si>
-    <t>Biologie moléculaire sur prélèvement Anapath</t>
-  </si>
-  <si>
-    <t>Analyse par des médecins anatomo-pathologistes des prélèvements, par biologie moléculaire avec des techniques ciblées (PCR, RT-PCR, hybridation in situ) ou plus larges (NGS) pour recherche de clonalité, de perte d'hétérozygotie, de mutations, de réarrangements, d'amplifications, à visée diagnostique, pronostique ou théranostique de certaines pathologies tumorales</t>
-  </si>
-  <si>
-    <t>446</t>
-  </si>
-  <si>
-    <t>Cytopathologie</t>
-  </si>
-  <si>
-    <t>Etude morphologique des cellules isolées, à partir de produits de ponction, brossage, frottis, aspiration, lavage</t>
-  </si>
-  <si>
-    <t>447</t>
-  </si>
-  <si>
-    <t>Histopathologie</t>
-  </si>
-  <si>
-    <t>Etude morphologique des tissus issus d'examen de prélevés par biopsie, ponction-biopsie, résection endoscopique et résection chirurgicale, avec pour objectif d'identifier les lésions provoquées par les maladies ou associées à celles-ci</t>
-  </si>
-  <si>
-    <t>448</t>
-  </si>
-  <si>
-    <t>Diagnostic lié à un retard ou Trouble du Neuro-Développement (TND)</t>
-  </si>
-  <si>
-    <t>Diagnostic pour répondre à des besoins relatifs au confort physique, la santé, le bien-être physique et mental.</t>
-  </si>
-  <si>
-    <t>449</t>
-  </si>
-  <si>
-    <t>Appui et coopération auprès des acteurs de l'enseignement</t>
-  </si>
-  <si>
-    <t>Soutien des acteurs de l'enseignement, spécialisé ou de droit commun, dans la prise en charge de l'élève, par l'apport d'une expertise et de ressources médico-sociales</t>
-  </si>
-  <si>
-    <t>450</t>
-  </si>
-  <si>
-    <t>Accompagnement à la réduction des risques en addictologie</t>
-  </si>
-  <si>
-    <t>Ensemble des pratiques qui visent à réduire les conséquences néfastes de l'addiction, tant au niveau sanitaire, psychologique que social. Cet accompagnement peut être initié par une première évaluation médico-psycho-sociale, et peut par exemple comprendre des ateliers de « pratiques à moindre risque » pour les usagers de drogues</t>
-  </si>
-  <si>
-    <t>451</t>
-  </si>
-  <si>
-    <t>Exploration et prise en charge des troubles du sommeil</t>
-  </si>
-  <si>
-    <t>Cette exploration consiste en des examens qui permettent d'enregistrer et d'analyser le sommeil au plan neurologique, respiratoire et cardiologique, ils comprennent entre autres la polysomnographie (correspond à l'exploration nocturne), des tests de maintien d'éveil et des tests de latence d'endormissement correspondent à l'exploration diurne</t>
-  </si>
-  <si>
-    <t>452</t>
-  </si>
-  <si>
-    <t>Exploration des troubles psycho-comportementaux et cognitifs</t>
-  </si>
-  <si>
-    <t>Cette exploration comprend une évaluation du fonctionnement cognitif globale (approche psychométrique) et spécifique (évaluation anatomoclinique, mnésique, cognitive, et écologique), une évaluation du comportement (échelles) et la restitution par un compte-rendu</t>
-  </si>
-  <si>
-    <t>453</t>
-  </si>
-  <si>
-    <t>Médecine et santé de l'adolescent</t>
-  </si>
-  <si>
-    <t>454</t>
-  </si>
-  <si>
-    <t>Radiologie polyvalente générale</t>
-  </si>
-  <si>
-    <t>Partie de la radiologie réalisant les actes généraux de base de radiologie au sens non hyperspécialisé.</t>
-  </si>
-  <si>
-    <t>455</t>
-  </si>
-  <si>
-    <t>Médecine thermale</t>
-  </si>
-  <si>
-    <t>Ensemble des activités médicales liées à l'utilisation et à l'exploitation des eaux thermales et leurs produits dérivés (gaz, boues), associant la thermalité (chaleur), les techniques de soins et des eaux thermales, à visée thérapeutique</t>
-  </si>
-  <si>
-    <t>456</t>
-  </si>
-  <si>
-    <t>Prise en charge médicale spécialisée des affections de l'appareil locomoteur permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections de l'appareil locomoteur sur l'état physique, fonctionnel, mental et social du patient.</t>
-  </si>
-  <si>
-    <t>457</t>
-  </si>
-  <si>
-    <t>Réunion de Concertation Pluridisciplinaire (RCP) Rhumatismes Inflammatoires Chroniques (RIC), maladies auto-immunes et biothérapies en rhumatologie</t>
-  </si>
-  <si>
-    <t>458</t>
-  </si>
-  <si>
-    <t>459</t>
-  </si>
-  <si>
-    <t>460</t>
-  </si>
-  <si>
-    <t>Réadaptation des affections endocrino-métaboliques et nutrition</t>
-  </si>
-  <si>
-    <t>461</t>
-  </si>
-  <si>
-    <t>462</t>
-  </si>
-  <si>
-    <t>463</t>
-  </si>
-  <si>
-    <t>Réadaptation des brulés</t>
-  </si>
-  <si>
-    <t>464</t>
-  </si>
-  <si>
-    <t>Réadaptation des evc-epr/etats de conscience minimaux</t>
-  </si>
-  <si>
-    <t>465</t>
-  </si>
-  <si>
-    <t>Réadaptation des fonctions sexuelles et de la reproduction</t>
-  </si>
-  <si>
-    <t>466</t>
-  </si>
-  <si>
-    <t>Chirurgie des varices</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie vasculaire qui consiste à traiter les maladies des veines superficielles des membres inférieurs ou du pelvis</t>
-  </si>
-  <si>
-    <t>467</t>
-  </si>
-  <si>
-    <t>Chirurgie orthopédique et traumatologique spécialisée main</t>
-  </si>
-  <si>
-    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme), spécialisé dans la chirurgie qui prend en charge les lésions de la main.</t>
-  </si>
-  <si>
-    <t>468</t>
-  </si>
-  <si>
-    <t>Chirurgie orthopédique et traumatologique spécialisée membres inférieurs</t>
-  </si>
-  <si>
-    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les lésions du membre inférieurs</t>
-  </si>
-  <si>
-    <t>469</t>
-  </si>
-  <si>
-    <t>Chirurgie orthopédique et traumatologique spécialisée membres supérieurs (sauf la main)</t>
-  </si>
-  <si>
-    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les lésions du membre supérieur en excluant la main.</t>
-  </si>
-  <si>
-    <t>470</t>
-  </si>
-  <si>
-    <t>Chirurgie orthopédique et traumatologique spécialisée tumeur</t>
-  </si>
-  <si>
-    <t>Partie de la chirurgie qui traite les déformations des os, des articulations, des muscles et des tendons et répare ceux qui sont abîmés au cours d'un accident (traumatisme) qui prends en charge les tumeurs malignes ou bénignes des os et des tissus mous du membre supérieur et de l'appareil locomoteur</t>
-  </si>
-  <si>
-    <t>471</t>
-  </si>
-  <si>
-    <t>Orientation vers un médecin traitant acceptant de nouveaux patients</t>
-  </si>
-  <si>
-    <t>Activité de coordination visant à orienter un patient, en fonction de ses besoins, vers un médecin traitant prenant de nouveaux patients, vers des soins « non programmés » (urgence non vitale) ou encore vers un professionnel de santé disponible (infirmier, dentiste etc.)</t>
-  </si>
-  <si>
-    <t>472</t>
-  </si>
-  <si>
-    <t>Veille et prévention de la récidive suicidaire</t>
-  </si>
-  <si>
-    <t>Ce dispositif consiste en un système de recontact et d'alerte en organisant autour de la personne ayant fait une tentative de suicide un réseau de professionnels de santé qui garderont le contact avec elle.</t>
-  </si>
-  <si>
-    <t>473</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique de la sphère oto-rhino-laryngée, cervico-faciale et maxillo-faciale</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses de la sphère oto-rhino-laryngée, cervico-faciale et maxillo-faciale.</t>
-  </si>
-  <si>
-    <t>474</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique viscérale et digestive</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie dont le périmètre d'intervention est l'ensemble des pathologies néoplasiques des organes digestifs et endocriniens, de l'oesophage jusqu'à l'anus.</t>
-  </si>
-  <si>
-    <t>475</t>
-  </si>
-  <si>
-    <t>Coordination de soins non-programmés</t>
-  </si>
-  <si>
-    <t>Organisation de la collaboration des professionnels de santé afin d'améliorer la prise en charge des patients d'une urgence ressentie par le patient, mais ne relevant pas nécessairement d'une urgence médicale à proprement dit.</t>
-  </si>
-  <si>
-    <t>476</t>
-  </si>
-  <si>
-    <t>Exploration fonctionnelle de l'audition</t>
-  </si>
-  <si>
-    <t>Examen(s) destiné(s) à explorer et mesurer le fonctionnement de l'audition.</t>
-  </si>
-  <si>
-    <t>477</t>
-  </si>
-  <si>
-    <t>Exploration fonctionnelle de la voix et de la déglutition</t>
-  </si>
-  <si>
-    <t>Examen(s) destiné(s) à apprécier la manière dont un organe assure sa fonction de phonation et de déglutition.</t>
-  </si>
-  <si>
-    <t>478</t>
-  </si>
-  <si>
-    <t>Exploration fonctionnelle des vertiges (audio vestibulaire)</t>
-  </si>
-  <si>
-    <t>Examen(s) destiné(s) à explorer et mesurer la fonction vestibulaire (otoneurologie).</t>
-  </si>
-  <si>
-    <t>479</t>
-  </si>
-  <si>
-    <t>Explorations fonctionnelles endocrinologie, diabétologie, métabolisme et nutrition</t>
-  </si>
-  <si>
-    <t>480</t>
-  </si>
-  <si>
-    <t>Médecine du sommeil</t>
-  </si>
-  <si>
-    <t>(= hypnologie ou somnologie) est la branche de la médecine spécialisée dans le diagnostic et le traitement des troubles de la vigilance (somnolence excessive) et du sommeil (insomnies, parasomnies).</t>
-  </si>
-  <si>
-    <t>481</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Allergologie</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Allergologie.</t>
-  </si>
-  <si>
-    <t>482</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Andrologie</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Andrologie.</t>
-  </si>
-  <si>
-    <t>483</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Diabétologie</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Diabétologie.</t>
-  </si>
-  <si>
-    <t>484</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Gériatrie, Gérontologie</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Gériatrie, Gérontologie.</t>
-  </si>
-  <si>
-    <t>485</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Gynécologie médicale</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Gynécologie médicale.</t>
-  </si>
-  <si>
-    <t>486</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Maladies infectieuses, parasitaires et tropicales</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Maladies infectieuses, parasitaires et tropicales.</t>
-  </si>
-  <si>
-    <t>487</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Médecine pédiatrique</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Médecine pédiatrique.</t>
-  </si>
-  <si>
-    <t>488</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Médecine vasculaire (Angiologie, Phlébologie)</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Médecine vasculaire (Angiologie, Phlébologie).</t>
-  </si>
-  <si>
-    <t>489</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Oncogériatrie (cancérologie)</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Oncogériatrie.</t>
-  </si>
-  <si>
-    <t>490</t>
-  </si>
-  <si>
-    <t>Médecine générale à orientation Pathologies osseuses médicales</t>
-  </si>
-  <si>
-    <t>Activité d'un médecin généraliste ayant acquis un diplôme ou une mention autorisée en Pathologies osseuses médicales.</t>
-  </si>
-  <si>
-    <t>491</t>
-  </si>
-  <si>
-    <t>Médecine gériatrique aiguë</t>
-  </si>
-  <si>
-    <t>492</t>
-  </si>
-  <si>
-    <t>Neuroradiologie interventionnelle</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau de la sphère cérébrale.</t>
-  </si>
-  <si>
-    <t>493</t>
-  </si>
-  <si>
-    <t>Psychomotricité</t>
-  </si>
-  <si>
-    <t>Aide fournie, sur prescription médicale, à des personnes souffrant de différents troubles psychomoteurs - c'est-à-dire confrontées à des difficultés psychologiques exprimées par le corps - en agissant sur leurs fonctions psychomotrices : difficultés d'attention, problèmes pour se repérer dans l'espace ou dans le temps.</t>
-  </si>
-  <si>
-    <t>494</t>
-  </si>
-  <si>
-    <t>Radiologie abdominale et digestive</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère digestive.</t>
-  </si>
-  <si>
-    <t>495</t>
-  </si>
-  <si>
-    <t>Radiologie cardio-vasculaire</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics au niveau du coeur et des vaisseaux.</t>
-  </si>
-  <si>
-    <t>496</t>
-  </si>
-  <si>
-    <t>Radiologie gynécologique</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère gynécologique.</t>
-  </si>
-  <si>
-    <t>497</t>
-  </si>
-  <si>
-    <t>Radiologie interventionnelle musculosquelettique</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau musculosquelettique.</t>
-  </si>
-  <si>
-    <t>498</t>
-  </si>
-  <si>
-    <t>Radiologie interventionnelle oncologique</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique de pathologies oncologiques.</t>
-  </si>
-  <si>
-    <t>499</t>
-  </si>
-  <si>
-    <t>Radiologie interventionnelle pédiatrique</t>
-  </si>
-  <si>
-    <t>500</t>
-  </si>
-  <si>
-    <t>Radiologie interventionnelle vasculaire</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes invasifs thérapeutiques et/ou diagnostics guidés par l'imagerie radiologique au niveau des vaisseaux sanguins.</t>
-  </si>
-  <si>
-    <t>501</t>
-  </si>
-  <si>
-    <t>Radiologie musculo-squelettique</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics au niveau musculo-squelettique.</t>
-  </si>
-  <si>
-    <t>502</t>
-  </si>
-  <si>
-    <t>Radiologie ORL et maxillo-faciale</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère ORL et maxillo-faciale.</t>
-  </si>
-  <si>
-    <t>503</t>
-  </si>
-  <si>
-    <t>Radiologie prénatale et pédiatrique</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics chez les enfants et en phase prénatale.</t>
-  </si>
-  <si>
-    <t>504</t>
-  </si>
-  <si>
-    <t>Radiologie sénologique (dont mammographie)</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics au niveau des seins.</t>
-  </si>
-  <si>
-    <t>505</t>
-  </si>
-  <si>
-    <t>Radiologie thoracique</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics au niveau thoracique.</t>
-  </si>
-  <si>
-    <t>506</t>
-  </si>
-  <si>
-    <t>Transplantation d'organe</t>
-  </si>
-  <si>
-    <t>Procédure thérapeutique qui vise à suppléer le fonctionnement défaillant d'un organe par un organe sain, appelé « greffon » ou « transplant » et provenant d'un donneur.</t>
-  </si>
-  <si>
-    <t>507</t>
-  </si>
-  <si>
-    <t>Uro-Radiologie</t>
-  </si>
-  <si>
-    <t>Réalisation d'actes radiologiques diagnostics au niveau de la sphère urogénitale.</t>
-  </si>
-  <si>
-    <t>508</t>
-  </si>
-  <si>
-    <t>Exploration fonctionnelle de l'exercice et du sport</t>
-  </si>
-  <si>
-    <t>Ensemble de tests permettant d'évaluer la capacité musculaire à l'effort à des fins de diagnostic, de suivi et de surveillance.</t>
-  </si>
-  <si>
-    <t>509</t>
-  </si>
-  <si>
-    <t>Traumatologie de l'activité physique et du sport</t>
-  </si>
-  <si>
-    <t>Prise en charge de l'ensemble des lésions macrotraumatiques et microtraumatiques de l'appareil locomoteur en lien avec la pratique de toute activité physique du niveau loisir au niveau compétition, qu'il s'agisse d'une lésion tendineuse, ligamentaire, osseuse ou cartilagineuse,</t>
-  </si>
-  <si>
-    <t>510</t>
-  </si>
-  <si>
-    <t>Échographie obstétricale de dépistage (1er, 2ème, 3ème trimestre)</t>
-  </si>
-  <si>
-    <t>Au premier trimestre : entre 11 semaines et 13 semaines d’aménorrhée et 6 jours (date du début de grossesse, identification et caractérisation des grossesses multiples, évaluation du risque d’anomalie chromosomique, dépistage de certaines pathologies). Au deuxième trimestre : entre 20 et 25 semaines d’aménorrhée (dépistage de certaines pathologies). Au troisième trimestre : entre 30 et 35 semaines d’aménorrhée (dépistage des retards de croissance intra-utérins et de certaines pathologies, localisation du placenta). Il est préférable de programmer ces examens au milieu de ces différentes périodes. Ces examens de dépistage échographique de première intention sont réalisés dans le cadre d’un suivi obstétrical de proximité, par des échographistes expérimentés dont le matériel répond aux normes définies par la nomenclature générale des actes professionnels. Les possibilités réelles et les limites de cet examen doivent être précisées à la femme enceinte ainsi que les informations disponibles dans le compte rendu d’échographie.</t>
-  </si>
-  <si>
-    <t>511</t>
-  </si>
-  <si>
-    <t>Accueil et hébergement spécialisé</t>
-  </si>
-  <si>
-    <t>Service qui vise à offrir à un enfant ou un adolescent handicapé un hébergement dans un environnement psychologique, éducatif et affectif complémentaire à celui qu'il peut trouver dans sa propre famille.</t>
-  </si>
-  <si>
-    <t>512</t>
-  </si>
-  <si>
-    <t>Accueil et orientation des victimes de violences sexuelles</t>
-  </si>
-  <si>
-    <t>Accueil, aide, soutien et soins aux victimes d'agressions sexuelles</t>
-  </si>
-  <si>
-    <t>513</t>
-  </si>
-  <si>
-    <t>Réadaptation locomotrice des patients amputés</t>
-  </si>
-  <si>
-    <t>514</t>
-  </si>
-  <si>
-    <t>Réadaptation PREcoce Post-Aiguë Cardiologique (PREPAC)</t>
-  </si>
-  <si>
-    <t>515</t>
-  </si>
-  <si>
-    <t>Réadaptation PREcoce Post-Aiguë Respiratoire (PREPAR)</t>
-  </si>
-  <si>
-    <t>516</t>
-  </si>
-  <si>
-    <t>Réadaptation neuro-orthopédique</t>
-  </si>
-  <si>
-    <t>517</t>
-  </si>
-  <si>
-    <t>Réadaptation PREcoce Post-Aiguë Neurologique (PREPAN)</t>
-  </si>
-  <si>
-    <t>518</t>
-  </si>
-  <si>
-    <t>Réadaptation des troubles cognitifs et comportementaux des patients cérébro-lésés</t>
-  </si>
-  <si>
-    <t>519</t>
-  </si>
-  <si>
-    <t>Réadaptation des affections médullaires</t>
-  </si>
-  <si>
-    <t>Prise en charge des affections médullaires permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections médullaires sur l'état physique, fonctionnel, mental et social du patient.</t>
-  </si>
-  <si>
-    <t>520</t>
-  </si>
-  <si>
-    <t>Réadaptation de l'obésité complexe</t>
-  </si>
-  <si>
-    <t>Branche des soins médicaux et de réadaptation qui vise à prévenir ou à réduire les conséquences fonctionnelles, les déficiences et les limitations d'activité liées à l'obésité complexe. L'obésité est considérée comme complexe lorsqu'elle présente l'un ou plusieurs des critères suivants : - Excès de poids majeur : indice de masse corporelle (IMC) - Evolution inquiétante de la courbe de corpulence : ascension extrême et continue - Comorbidités sévères associées au surpoids ou à l'obésité : i.e. respiratoires, articulaires, métaboliques, psychologiques ou sociales (harcèlement en milieu scolaire) ; - Antécédents d'échecs thérapeutiques ; - Situation de fragilité : difficultés psychosociales, famille non-aidante, handicap physique et/ou psychique dû à la sévérité de l'obésité, handicap physique non dû à l'obésité mais aggravé par celle-ci, pathologie psychiatrique (utilisation de psychotropes), pathologie chronique (rénale, cardiaque, osseuses, ou autres) aggravée par l'obésité, déficit cognitif, troubles du comportement, pathologie psychiatrique ; - Obésité syndromique identifiée (exemple du syndrome de Prader-Willi) ou non.</t>
-  </si>
-  <si>
-    <t>521</t>
-  </si>
-  <si>
-    <t>Réadaptation des troubles cognitifs sévères liés à une conduite addictive</t>
-  </si>
-  <si>
-    <t>522</t>
-  </si>
-  <si>
-    <t>Réadaptation polyhandicap</t>
-  </si>
-  <si>
-    <t>Prise en charge du polyhandicap permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections liées au polyhandicap sur l'état physique, fonctionnel, mental et social du patient.</t>
-  </si>
-  <si>
-    <t>523</t>
-  </si>
-  <si>
-    <t>Réadaptation des affections oncologiques</t>
-  </si>
-  <si>
-    <t>524</t>
-  </si>
-  <si>
-    <t>Réadaptation troubles du langage et des apprentissages</t>
-  </si>
-  <si>
-    <t>525</t>
-  </si>
-  <si>
-    <t>Evaluation et orientation des auteurs de violences sexuelles</t>
-  </si>
-  <si>
-    <t>526</t>
-  </si>
-  <si>
-    <t>Informer, évaluer, accompagner et orienter dans le cadre d'une orientation professionnelle</t>
-  </si>
-  <si>
-    <t>527</t>
-  </si>
-  <si>
-    <t>Suivi gynécologique de prévention et contraception</t>
-  </si>
-  <si>
-    <t>Consultation gynécologique qui permet les frottis, le dépistage, la prescription d'examens, la prescription de tous les moyens de contraception, de poser et retirer un stérilet ou un implant contraceptif, de pratiquer les IVG médicamenteuses, et de vacciner l'entourage de la femme et du nouveau-né.</t>
-  </si>
-  <si>
-    <t>528</t>
-  </si>
-  <si>
-    <t>Suivi neuropsychologique</t>
-  </si>
-  <si>
-    <t>Ensemble des examens, tests et épreuves psychométriques qui permettent de déterminer le retentissement cognitivo-comportemental d'une pathologie connue, de contribuer au diagnostic, ou de contribuer à une expertise médico-légale.</t>
-  </si>
-  <si>
-    <t>529</t>
-  </si>
-  <si>
-    <t>Suivi post-natal (dont séances post-natales)</t>
-  </si>
-  <si>
-    <t>Actions de prévention et de suivi éducatif en cas de besoin particulier décelé pendant la grossesse ou après l'accouchement chez les parents ou chez l'enfant réalisé par les sages-femmes.</t>
-  </si>
-  <si>
-    <t>530</t>
-  </si>
-  <si>
-    <t>Suivi prénatal (suivi de grossesse)</t>
-  </si>
-  <si>
-    <t>Consultations et examens complémentaires qui permettent le suivi de la grossesse normale et l'amélioration de l'identification des situations à risques de complications maternelles, obstétricales et foetales pouvant potentiellement compliquer la grossesse (hors accouchement) afin d'en adapter si besoin le suivi.</t>
-  </si>
-  <si>
-    <t>531</t>
-  </si>
-  <si>
-    <t>Réadaptation viroses chroniques</t>
-  </si>
-  <si>
-    <t>Prise en charge des affections chroniques secondaires à une virose permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections sur l'état physique, fonctionnel, mental et social du patient.</t>
-  </si>
-  <si>
-    <t>532</t>
-  </si>
-  <si>
-    <t>Réadaptation lymphologie</t>
-  </si>
-  <si>
-    <t>Prise en charge des affections dues au lymphoedème permettant de prévenir ou de réduire au minimum les conséquences des traumatismes ou des affections sur l'état physique, fonctionnel, mental et social du patient.</t>
-  </si>
-  <si>
-    <t>533</t>
-  </si>
-  <si>
-    <t>Accession à un logement individuel</t>
-  </si>
-  <si>
-    <t>534</t>
-  </si>
-  <si>
-    <t>Accompagnement infirmier pour téléconsultation médicale</t>
-  </si>
-  <si>
-    <t>535</t>
-  </si>
-  <si>
-    <t>Sexologie clinique</t>
-  </si>
-  <si>
-    <t>Etude de la sexualité et de la fonction érotique qui prend en charge les problématiques sexuelles psychologiques, éducationnelles, relationnelles et comportementales</t>
-  </si>
-  <si>
-    <t>536</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique thoracique</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses thoraciques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>537</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique urologique</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses urologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>538</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique gynécologique</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses gynécologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>539</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique mammaire</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses mammaires. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>540</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique neurologique</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses neurologiques (intra-crannienne et/ou intra-rachidienne). Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>541</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique ophtalmologique</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses ophtalmologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>542</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique dermatologique</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses dermatologiques. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>543</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique des os et des tissus mous</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses des os et des tissus mous. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>544</t>
-  </si>
-  <si>
-    <t>Chirurgie oncologique de la thyroïde</t>
-  </si>
-  <si>
-    <t>Branche de la chirurgie qui s'intéresse aux tumeurs cancéreuses de la thyroïde. Elle comprend la chirurgie conservatrice, le curage ganglionnaire, la chirurgie radicale, la chirurgie de résection tumorale macroscopiquement complète en cas de carcinose péritonéale, la chirurgie des métastases, les techniques de destruction tumorale non percutanée, la chirurgie de reconstruction immédiate dans le même temps opératoire que l'exérèse, ainsi que la chirurgie de la récidive.</t>
-  </si>
-  <si>
-    <t>545</t>
-  </si>
-  <si>
-    <t>Chimiothérapie intensive</t>
-  </si>
-  <si>
-    <t>546</t>
-  </si>
-  <si>
-    <t>Exploration et prise en charge de la dénutrition</t>
-  </si>
-  <si>
-    <t>Diagnostic et prise en charge d'un état d'un organisme en déséquilibre nutritionnel », le déséquilibre étant caractérisé par un bilan énergétique et/ou protéique négatif soit par un déficit d'apport isolé, une augmentation des dépenses ou des pertes, soit une association d'un déficit d'apport avec une augmentation des dépenses ou des pertes.</t>
-  </si>
-  <si>
-    <t>547</t>
-  </si>
-  <si>
-    <t>Evaluation de situation sociale préoccupante</t>
-  </si>
-  <si>
-    <t>548</t>
-  </si>
-  <si>
-    <t>Coordination de parcours (Care management)</t>
-  </si>
-  <si>
-    <t>549</t>
-  </si>
-  <si>
-    <t>Diététique et nutrition</t>
-  </si>
-  <si>
-    <t>Dispensation des conseils nutritionnels  l’éducation et à la rééducation nutritionnelle des patients atteints de troubles du métabolisme ou de l’alimentation, par l’établissement d’un bilan diététique personnalisé et une éducation diététique adaptée. Les diététiciens contribuent à la définition, à l’évaluation et au contrôle de la qualité de l’alimentation servie en collectivité, ainsi qu’aux activités de prévention en santé publique relevant du champ de la nutrition.</t>
-  </si>
-  <si>
-    <t>550</t>
-  </si>
-  <si>
-    <t>Accompagnement puériculteur à la périnatalité</t>
-  </si>
-  <si>
-    <t>551</t>
-  </si>
-  <si>
-    <t>Génétique chromosomique</t>
-  </si>
-  <si>
-    <t>552</t>
-  </si>
-  <si>
-    <t>Génétique moléculaire</t>
-  </si>
-  <si>
-    <t>553</t>
-  </si>
-  <si>
-    <t>Suivi socio-éducatif</t>
-  </si>
-  <si>
-    <t>554</t>
-  </si>
-  <si>
-    <t>Promotion de la santé de l'enfant</t>
-  </si>
-  <si>
-    <t>555</t>
-  </si>
-  <si>
-    <t>Soins infirmiers orientation Onco-hématologie</t>
-  </si>
-  <si>
-    <t>556</t>
-  </si>
-  <si>
-    <t>Soins infirmiers en puériculture</t>
-  </si>
-  <si>
-    <t>Ensemble des interventions réalisées par des infirmiers spécialisés diplômés pour promouvoir, maintenir et restaurer la santé des nourrissons, des jeunes enfants et des mères. Ces interventions englobent la prévention, le suivi du développement de l'enfant, l'accompagnement des familles, et les soins spécifiques liés aux pathologies pédiatriques.</t>
-  </si>
-  <si>
-    <t>557</t>
-  </si>
-  <si>
-    <t>Suivi du développement de l'enfant</t>
-  </si>
-  <si>
-    <t>Evaluation continue par un professionnel de santé visant à surveiller la croissance physique, cognitive, émotionnelle et sociale de l'enfant, afin de s'assurer qu'il atteint les étapes clés de son développement en fonction de son âge. Ce suivi permet de dépister précocement d'éventuels retards ou troubles, d'intervenir rapidement si nécessaire et d'accompagner les parents dans leur rôle éducatif et de soutien.</t>
-  </si>
-  <si>
-    <t>558</t>
-  </si>
-  <si>
-    <t>Ergothérapie</t>
-  </si>
-  <si>
-    <t>Activité professionelle qui contribue, par la rééducation, la réadaptation et la réinsertion, au traitement des déficiences, des incapacités et des situations de handicap</t>
-  </si>
-  <si>
-    <t>559</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Fonctions sexuelles et de la reproduction</t>
-  </si>
-  <si>
-    <t>560</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Obésité complexe</t>
-  </si>
-  <si>
-    <t>561</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Cancérologie</t>
-  </si>
-  <si>
-    <t>562</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Pédiatrie</t>
-  </si>
-  <si>
-    <t>563</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Soins palliatifs</t>
-  </si>
-  <si>
-    <t>564</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Santé mentale</t>
-  </si>
-  <si>
-    <t>565</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Maxillo-faciale</t>
-  </si>
-  <si>
-    <t>566</t>
-  </si>
-  <si>
-    <t>Kinésithérapie orientation Gestion de la douleur</t>
-  </si>
-  <si>
-    <t>567</t>
-  </si>
-  <si>
-    <t>Soins infirmiers orientation Gestion de la douleur</t>
-  </si>
-  <si>
-    <t>568</t>
-  </si>
-  <si>
-    <t>Soins infirmiers orientation Santé mentale</t>
-  </si>
-  <si>
-    <t>569</t>
-  </si>
-  <si>
-    <t>Soins infirmiers orientation Cardiologie</t>
-  </si>
-  <si>
-    <t>570</t>
-  </si>
-  <si>
-    <t>Soins infirmiers orientation Respiratoire</t>
-  </si>
-  <si>
-    <t>571</t>
-  </si>
-  <si>
-    <t>Soins infirmiers orientation Soins palliatifs</t>
-  </si>
-  <si>
-    <t>572</t>
-  </si>
-  <si>
-    <t>Soins infirmiers orientation Neurologie</t>
-  </si>
-  <si>
-    <t>573</t>
-  </si>
-  <si>
-    <t>Soins infirmiers orientation Diabète</t>
-  </si>
-  <si>
-    <t>574</t>
-  </si>
-  <si>
-    <t>Ergothérapie orientation accompagnement dans le cadre des maladies chroniques</t>
-  </si>
-  <si>
-    <t>Accompagnement en ergothérapie centré sur l’impact de maladies chroniques (affection de longue durée qui évolue dans le temps, souvent lentement, et qui a un impact durable sur la vie quotidienne de la personne) dans le quotidien de la personne : gestion de la fatigue et/ou la gestion de la douleur et/ou la gestion du sommeil en lien avec les activités de vie la personne dans son environnement. Il vise à favoriser la qualité de vie, l’équilibre de vie.</t>
-  </si>
-  <si>
-    <t>575</t>
-  </si>
-  <si>
-    <t>Ergothérapie orientation compensation matérielle dans l’environnement de la personne</t>
-  </si>
-  <si>
-    <t>Accompagnement en ergothérapie de personnes dans l’accès à l'ensemble des aides techniques, équipements et aménagements destinés à compenser une perte de fonction, une limitation d’activité ou une situation de handicap. Cela inclus l’apprentissage d’utilisation des compensations matérielles et la prise en compte de l’environnement de la personne jusqu’à intervenir dans celui-ci.</t>
-  </si>
-  <si>
-    <t>576</t>
-  </si>
-  <si>
-    <t>Ergothérapie orientation Gériatrie</t>
-  </si>
-  <si>
-    <t>Accompagnement en ergothérapie concerne la prise en charge des personnes âgées, notamment celles confrontées à des pertes d’autonomie, des pathologies chroniques ou neurodégénératives (comme la maladie d'Alzheimer, Parkinson, ou des troubles cognitifs), ainsi qu'à la prévention du vieillissement pathologique. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
-  </si>
-  <si>
-    <t>577</t>
-  </si>
-  <si>
-    <t>Ergothérapie orientation Neurologie</t>
-  </si>
-  <si>
-    <t>Accompagnement en ergothérapie auprès de personnes avec des pathologies neurologiques innées ou acquises (dépistage ; repérage ; évaluation permettant le diagnostic ergothérapique ; réévaluation). Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle.</t>
-  </si>
-  <si>
-    <t>578</t>
-  </si>
-  <si>
-    <t>Ergothérapie orientation Pédiatrie</t>
-  </si>
-  <si>
-    <t>Accompagnement en ergothérapie des enfants, de la naissance à l’adolescence, présentant des troubles du développement, des déficiences physiques, sensorielles, cognitives ou psychiques, ainsi que des situations de handicap, afin de favoriser leur autonomie et leur participation dans les activités de la vie quotidienne, scolaire et sociale. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle.</t>
-  </si>
-  <si>
-    <t>579</t>
-  </si>
-  <si>
-    <t>Ergothérapie orientation Psychiatrie et Santé mentale</t>
-  </si>
-  <si>
-    <t>Accompagnement en ergothérapie  concerne l’accompagnement des personnes présentant des troubles psychiques ou psychiatriques afin de favoriser leur autonomie, leur bien-être et leur inclusion sociale. L’ergothérapeute intervient en évaluant et en renforçant les capacités fonctionnelles, cognitives, émotionnelles et sociales des patients dans le cadre d’un projet thérapeutique global. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
-  </si>
-  <si>
-    <t>580</t>
-  </si>
-  <si>
-    <t>Evaluation en ergothérapie par l’analyse d’activité et accompagnement dans l’environnement de la personne</t>
-  </si>
-  <si>
-    <t>Evaluation fonctionnelle et accompagnement en ergothérapie au travers de mises en situation d’activité réelles (via l’analyse d’activité) en milieu écologique (sur l’ensemble des lieux de vie ((domicile, établissements médico-sociaux, etc.) et d’activité de la personne (établissements scolaires, lieux de formation, milieu professionnel, milieu sportif, de loisirs, etc.)</t>
-  </si>
-  <si>
-    <t>581</t>
-  </si>
-  <si>
-    <t>Interventions éducatives pour renforcer l’autorégulation</t>
-  </si>
-  <si>
-    <t>Consiste à mettre en place des stratégies et des activités visant à aider les personnes, notamment les enfants et les adolescents, à mieux gérer leurs émotions, leurs comportements et leurs pensées. Ces interventions sont particulièrement utiles pour les élèves présentant des troubles du spectre de l'autisme (TSA) et d'autres troubles du neurodéveloppement. Elles sont encadrées par des professionnels, et s'appuient sur des principes de métacognition et d'autodétermination. Cette orientation est étayée par la réalisation de formations continues spécifiques auprès de cette population (appuyées de données probantes) et d’une expérience professionnelle</t>
-  </si>
-  <si>
-    <t>582</t>
-  </si>
-  <si>
-    <t>Orientation vers professionnel pour diagnostic</t>
-  </si>
-  <si>
-    <t>583</t>
-  </si>
-  <si>
-    <t>Technique d’épuration extrarénale réalisée au domicile ou en établissement, qui utilise le péritoine comme membrane de dialyse après injection d’une solution de dialyse dans la cavité abdominale, elle constitue une alternative à l’hémodialyse, permettant une autonomie accrue du patient et une efficacité comparable en termes de survie et de qualité de vie.</t>
-  </si>
-  <si>
-    <t>584</t>
-  </si>
-  <si>
-    <t>Diététique des Troubles des Conduites Alimentaires (TCA)</t>
-  </si>
-  <si>
-    <t>Prise en soin diététique  des troubles du comportement alimentaire (anorexie, boulimie, hyperphagie) comprenant  la régulation alimentaire, l’image corporelle et les émotions.</t>
-  </si>
-  <si>
-    <t>585</t>
-  </si>
-  <si>
-    <t>Diététique orientation Dénutrition</t>
-  </si>
-  <si>
-    <t>Accompagnement des patients à risque ou en situation de dénutrition pour prévenir ou corriger les déficits nutritionnels.</t>
-  </si>
-  <si>
-    <t>586</t>
-  </si>
-  <si>
-    <t>Diététique orientation Gynécologie / Obstétrique</t>
-  </si>
-  <si>
-    <t>Prise en charge nutritionnelle des femmes tout au long de leur parcours gynécologique et obstétrique, comprennant  notamment la grossesse, aux parturientes présentant des pathologies spécifiques (diabète gestationnel, troubles métaboliques, surpoids, dénutrition, etc.) ou gynécologique (SOPK, endométriose, ménopause) ou leur grossesse.</t>
-  </si>
-  <si>
-    <t>587</t>
-  </si>
-  <si>
-    <t>Diététique orientation maladies inflammatoires et malabsorptives (MICI, SII, NASH)</t>
-  </si>
-  <si>
-    <t>Prise en charge nutritionnelle individualisée visant à limiter les symptômes, prévenir les carences et adapter l’alimentation selon les phases évolutives de pathologies digestives inflammatoire chroniques.</t>
-  </si>
-  <si>
-    <t>588</t>
-  </si>
-  <si>
-    <t>Diététique orientation Nutrition du sportif</t>
-  </si>
-  <si>
-    <t>Optimisation de l’alimentation pour soutenir la performance, la récupération et la prévention des blessures, chez le sportif  en lien avec les objectifs et le niveau de pratique.</t>
-  </si>
-  <si>
-    <t>589</t>
-  </si>
-  <si>
-    <t>Diététique orientation Périnatalité</t>
-  </si>
-  <si>
-    <t>Soutien nutritionnel dans le cadre du projet parental, de la grossesse, de l’allaitement, et de la diversification alimentaire du nourrisson.</t>
-  </si>
-  <si>
-    <t>590</t>
-  </si>
-  <si>
-    <t>Échographie gynécologique</t>
-  </si>
-  <si>
-    <t>L’échographie gynécologique est un examen d’imagerie médicale par ultrasons destiné à explorer les organes pelviens féminins (principalement l’utérus, l’endomètre, les ovaires, les trompes et les structures annexielles) en dehors du suivi obstétrical. Elle est réalisée par voie endovaginale et/ou par voie sus-pubienne afin de rechercher, caractériser ou suivre des anomalies anatomiques ou pathologiques gynécologiques (telles que kystes ovariens, fibromes, adénomyose, endométriose, etc.) et contribuer à la prise en charge clinique adaptée de la patiente.</t>
-  </si>
-  <si>
-    <t>591</t>
-  </si>
-  <si>
-    <t>Ostéopathie médicale</t>
-  </si>
-  <si>
-    <t>Pratique médicale (réservée aux médecins), utilisant des techniques manuelles de manipulations musculo-squelettiques à visée diagnostique et thérapeutique. L’ostéopathie médicale est reconnue comme acte médical par le Conseil national de l’Ordre des médecins</t>
-  </si>
-  <si>
-    <t>592</t>
-  </si>
-  <si>
-    <t>Prévention et lutte contre la tuberculose</t>
-  </si>
-  <si>
-    <t>593</t>
-  </si>
-  <si>
-    <t>Prise en charge coordonnée des patients atteints de maladies rares</t>
-  </si>
-  <si>
-    <t>Organisation de soins qui dispense  pour les personnes atteintes de maladies rares, un accompagnement pluridisciplinaire, depuis le diagnostic jusqu’au suivi, impliquant professionnels spécialisés, de proximité, médico-social, social et associations.</t>
-  </si>
-  <si>
-    <t>594</t>
-  </si>
-  <si>
-    <t>Coordination hospitalière de prélèvement de tissu</t>
-  </si>
-  <si>
-    <t>Activité hospitalière spécialisée qui coordonne l’ensemble des prélèvements de tissu (et d’organe), assure le recueil de la non-opposition, l’accompagnement des proches, la traçabilité, la sécurité sanitaire et le respect des règles légales et éthiques.</t>
-  </si>
-  <si>
-    <t>595</t>
-  </si>
-  <si>
-    <t>Coordination hospitalière de prélèvement de tissu pédiatrique</t>
-  </si>
-  <si>
-    <t>Activité hospitalière spécialisée qui organise le prélèvement de tissu chez des enfants (vivants ou décédés), la recherche du consentement éclairé des représentants légaux, la traçabilité, et les règles juridiques et éthiques propres au don de tissus.</t>
-  </si>
-  <si>
-    <t>596</t>
-  </si>
-  <si>
-    <t>Coordination hospitalière de prélèvement d’organe pédiatrique</t>
-  </si>
-  <si>
-    <t>Activité hospitalière spécialisée qui identifie, mobilise et coordonne les prélèvements d’organes chez les enfants, en assurant le recueil du consentement légal, la conformité aux règles éthiques, la traçabilité et la liaison entre les équipes de greffe et les proches.</t>
-  </si>
-  <si>
-    <t>597</t>
-  </si>
-  <si>
-    <t>Evaluation de la mémoire (bilan mémoire)</t>
-  </si>
-  <si>
-    <t>Evaluation clinique spécialisée qui mesure de façon formelle les capacités mnésiques  (encodage, stockage, restitution ) et recherche leur retentissement sur la vie quotidienne, à l’aide de tests validés, d’un entretien, et d’examens complémentaires afin de poser un diagnostic ou d’orienter vers une prise en charge adaptée.</t>
-  </si>
-  <si>
-    <t>598</t>
-  </si>
-  <si>
-    <t>Toxicologie clinique</t>
-  </si>
-  <si>
-    <t>599</t>
-  </si>
-  <si>
-    <t>Analyse toxicologique</t>
-  </si>
-  <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>Prise en charge des malaises et surdoses liés à la prise de drogues</t>
-  </si>
-  <si>
-    <t>601</t>
-  </si>
-  <si>
-    <t>Médiation pour le maintien en hospitalisation</t>
-  </si>
-  <si>
-    <t>602</t>
-  </si>
-  <si>
-    <t>Pair aidance pour l'autodétermination</t>
-  </si>
-  <si>
-    <t>603</t>
-  </si>
-  <si>
-    <t>Prise en charge coordonnée des patients atteints de maladies neurodégénératives</t>
-  </si>
-  <si>
-    <t>604</t>
-  </si>
-  <si>
-    <t>Chirurgie pédiatrique spécialisée orthopédique</t>
-  </si>
-  <si>
-    <t>605</t>
-  </si>
-  <si>
-    <t>Chirurgie pédiatrique spécialisée digestif et viscérale</t>
-  </si>
-  <si>
-    <t>606</t>
-  </si>
-  <si>
-    <t>Accompagnement pour l’autodétermination de la personne</t>
-  </si>
-  <si>
-    <t>607</t>
-  </si>
-  <si>
-    <t>Fonction-ressource : expertise-conseils auprès des acteurs du secteur sanitaire</t>
-  </si>
-  <si>
-    <t>608</t>
-  </si>
-  <si>
-    <t>Fonction-ressource : expertise-conseils auprès des acteurs du milieu ordinaire</t>
-  </si>
-  <si>
-    <t>609</t>
-  </si>
-  <si>
-    <t>Fonction-ressource : expertise-conseils auprès de acteurs du secteur judiciaire</t>
-  </si>
-  <si>
-    <t>610</t>
-  </si>
-  <si>
-    <t>Pédiatrie spécialisée neurologie</t>
-  </si>
-  <si>
-    <t>611</t>
-  </si>
-  <si>
-    <t>Pédiatrie spécialisée pneumologie</t>
-  </si>
-  <si>
-    <t>612</t>
-  </si>
-  <si>
-    <t>Psychiatrie de crise</t>
-  </si>
-  <si>
-    <t>Activité de soins psychiatriques qui assure une prise en charge immédiate des situations de crise psychique aiguë, caractérisées par une souffrance intense ou un risque pour la personne, afin de prévenir une aggravation ou une hospitalisation non adaptée. Elle s’appuie sur des interventions brèves, coordonnées et pluridisciplinaires, en lien avec les dispositifs d’urgence.</t>
-  </si>
-  <si>
-    <t>613</t>
-  </si>
-  <si>
-    <t>Echographie obstétricale de diagnostic</t>
-  </si>
-  <si>
-    <t>En cas d’aspect inhabituel (morphologique et/ou biométrique), de doute ou de difficulté persistante à fournir les éléments demandés pour l’examen de dépistage. Cet examen de deuxième rang est réalisé par des praticiens ayant une expérience et une expertise spécifiques et exerçant en relation avec un (ou plusieurs) Centre(s) Pluridisciplinaire(s) de Diagnostic Prénatal.</t>
-  </si>
-  <si>
-    <t>614</t>
-  </si>
-  <si>
-    <t>Soins infirmiers en pratique avancée en pathologies chroniques stabilisées</t>
-  </si>
-  <si>
-    <t>615</t>
-  </si>
-  <si>
-    <t>Soins infirmiers en pratique avancée en oncologie et hémato-oncologie</t>
-  </si>
-  <si>
-    <t>616</t>
-  </si>
-  <si>
-    <t>Soins infirmiers en pratique avancée en maladie rénale chronique</t>
-  </si>
-  <si>
-    <t>617</t>
-  </si>
-  <si>
-    <t>Soins infirmiers en pratique avancée en santé mentale</t>
-  </si>
-  <si>
-    <t>618</t>
-  </si>
-  <si>
-    <t>Collecte de don de lait maternel cru</t>
-  </si>
-  <si>
-    <t>619</t>
-  </si>
-  <si>
-    <t>Distribution de lait maternel pasteurisé</t>
-  </si>
-  <si>
-    <t>620</t>
-  </si>
-  <si>
-    <t>Bilan psychomoteur</t>
-  </si>
-  <si>
-    <t>621</t>
-  </si>
-  <si>
-    <t>Soin psychomoteur</t>
-  </si>
-  <si>
-    <t>622</t>
-  </si>
-  <si>
-    <t>Education psychomotrice (pédagogie du développement psychomoteur)</t>
-  </si>
-  <si>
-    <t>623</t>
-  </si>
-  <si>
-    <t>Stimulation psychomotrice (stimulation du fonctionnement psychomoteur à visée préventive)</t>
-  </si>
-  <si>
-    <t>624</t>
-  </si>
-  <si>
-    <t>Rééducation de la graphomotricité et de l’écriture (dysgraphie)</t>
-  </si>
-  <si>
-    <t>625</t>
-  </si>
-  <si>
-    <t>Orthoptie : orientation troubles neuro-visuels (pathologies neurologiques, maladies neurodégénératives)</t>
-  </si>
-  <si>
-    <t>626</t>
-  </si>
-  <si>
-    <t>Orthoptie orientation basse vision</t>
-  </si>
-  <si>
-    <t>627</t>
-  </si>
-  <si>
-    <t>Orthoptie orientation pédiatrique</t>
-  </si>
-  <si>
-    <t>628</t>
   </si>
   <si>
     <t>Conseil et accompagnement dans la gestion des traitements</t>
@@ -12943,7 +12946,7 @@
         <v>1509</v>
       </c>
       <c r="C629" t="s" s="2">
-        <v>879</v>
+        <v>1510</v>
       </c>
       <c r="D629" s="2"/>
     </row>
@@ -12955,7 +12958,7 @@
         <v>34</v>
       </c>
       <c r="C630" t="s" s="2">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="D630" s="2"/>
     </row>
